--- a/momentum/ETFs/etf_rankings.xlsx
+++ b/momentum/ETFs/etf_rankings.xlsx
@@ -861,7 +861,7 @@
         <v>36.0477501703408</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>11.74285714285714</v>
+        <v>9.521142537104454</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>2.587885919481731</v>
@@ -930,7 +930,7 @@
         <v>100.8931125031753</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>21.5028215028215</v>
+        <v>22.85285285285286</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>2.409829391027872</v>
@@ -1003,7 +1003,7 @@
         <v>10.27335657280187</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>16.81592039800994</v>
+        <v>12.55992329817834</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>2.119599627295667</v>
@@ -1076,7 +1076,7 @@
         <v>98.7865593330821</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6.850000000000001</v>
+        <v>6.307830066660025</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>1.964824078457934</v>
@@ -1149,7 +1149,7 @@
         <v>233.9747237878053</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>23.85764878638679</v>
+        <v>21.42433736980267</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>1.809315469142009</v>
@@ -1222,7 +1222,7 @@
         <v>11.51211590841348</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>15.8176943699732</v>
+        <v>13.88400702987698</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>1.499121109419864</v>
@@ -1295,7 +1295,7 @@
         <v>11.52659113059735</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>13.68421052631579</v>
+        <v>13.784021071115</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>1.472132231703636</v>
@@ -1368,7 +1368,7 @@
         <v>36.02111017033209</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>11.50114155251143</v>
+        <v>9.31729155008394</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>1.461747498313979</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n">
-        <v>16.12903225806452</v>
+        <v>14.0726933830382</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>1.434718521984453</v>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n">
-        <v>24.24916573971079</v>
+        <v>17.33193277310925</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>1.426946458032408</v>
@@ -1575,7 +1575,7 @@
         <v>46.50322445222943</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>24.4039270687237</v>
+        <v>17.45751489737364</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>1.114003771915568</v>
@@ -1648,7 +1648,7 @@
         <v>79.55869184947483</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>22.35783633841888</v>
+        <v>15.81987659183406</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.9993359730462348</v>
@@ -1721,7 +1721,7 @@
         <v>31.92340267987092</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>10.84612871610584</v>
+        <v>8.298755186722007</v>
       </c>
       <c r="M16" s="13" t="n">
         <v>0.9838238195907922</v>
@@ -1794,7 +1794,7 @@
         <v>15.06882232720338</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>11.35888501742162</v>
+        <v>7.681940700808632</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.969477771975843</v>
@@ -1867,7 +1867,7 @@
         <v>87.31276210421984</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>23.08769250350007</v>
+        <v>15.65414972494617</v>
       </c>
       <c r="M18" s="13" t="n">
         <v>0.9583815914272557</v>
@@ -1940,7 +1940,7 @@
         <v>10.32081438282395</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>10.68548387096775</v>
+        <v>8.712871287128721</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0.9015270281536603</v>
@@ -2013,7 +2013,7 @@
         <v>96.546041669602</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>10.95608911961932</v>
+        <v>8.080488832701228</v>
       </c>
       <c r="M20" s="13" t="n">
         <v>0.8900905545445528</v>
@@ -2086,7 +2086,7 @@
         <v>119.0376963887748</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>9.809599017285265</v>
+        <v>7.397236763065318</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>0.8418551892331569</v>
@@ -2159,7 +2159,7 @@
         <v>101.232387650885</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>12.78132523814508</v>
+        <v>8.608870967741922</v>
       </c>
       <c r="M22" s="13" t="n">
         <v>0.8092555965181292</v>
@@ -2232,7 +2232,7 @@
         <v>9.563165939602666</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>14.12300683371299</v>
+        <v>9.031556039173005</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0.6982167380038752</v>
@@ -2301,7 +2301,7 @@
         <v>15.79458076819297</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>14.61377870563674</v>
+        <v>10.16722408026756</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>0.5823936403414288</v>
@@ -2370,7 +2370,7 @@
         <v>59.06561704270673</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>14.9075081610446</v>
+        <v>11.09942135718043</v>
       </c>
       <c r="M25" s="13" t="n">
         <v>0.5770735917841835</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K26" s="12" t="n"/>
       <c r="L26" s="12" t="n">
-        <v>11.02150537634408</v>
+        <v>10.42780748663101</v>
       </c>
       <c r="M26" s="13" t="n">
         <v>0.5062801260866725</v>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n">
-        <v>16.79518815545959</v>
+        <v>10.31318281136198</v>
       </c>
       <c r="M27" s="13" t="n">
         <v>0.5005117023119937</v>
@@ -2577,7 +2577,7 @@
         <v>9.118306597702359</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>15.38461538461537</v>
+        <v>9.50173812282733</v>
       </c>
       <c r="M28" s="13" t="n">
         <v>0.4529079872672848</v>
@@ -2646,7 +2646,7 @@
         <v>69.49235500216736</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>9.47058823529412</v>
+        <v>7.185025197984163</v>
       </c>
       <c r="M29" s="13" t="n">
         <v>0.4508714834265253</v>
@@ -2719,7 +2719,7 @@
         <v>143.1946106746558</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3.868943882886033</v>
+        <v>5.003523608174776</v>
       </c>
       <c r="M30" s="13" t="n">
         <v>0.4503353048516891</v>
@@ -2792,7 +2792,7 @@
         <v>144.7312340382067</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>3.213675213675216</v>
+        <v>4.862799583188604</v>
       </c>
       <c r="M31" s="13" t="n">
         <v>0.4259231450785703</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="K32" s="12" t="n"/>
       <c r="L32" s="12" t="n">
-        <v>16.70790037935017</v>
+        <v>10.37279675557636</v>
       </c>
       <c r="M32" s="13" t="n">
         <v>0.4173727600558846</v>
@@ -2932,7 +2932,7 @@
         <v>120.6566699090284</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>3.251965923984268</v>
+        <v>5.02416263956007</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>0.3970893923996646</v>
@@ -3005,7 +3005,7 @@
         <v>13.55309182552233</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>3.526818515797214</v>
+        <v>4.992548435171384</v>
       </c>
       <c r="M34" s="13" t="n">
         <v>0.3955895232520931</v>
@@ -3078,7 +3078,7 @@
         <v>140.3103062758128</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>3.534817956875225</v>
+        <v>5.625676163000337</v>
       </c>
       <c r="M35" s="13" t="n">
         <v>0.3904616228278521</v>
@@ -3151,7 +3151,7 @@
         <v>12583.42464395361</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3.315218239235773</v>
+        <v>4.308748295198472</v>
       </c>
       <c r="M36" s="13" t="n">
         <v>0.3903525261822038</v>
@@ -3224,7 +3224,7 @@
         <v>123.9928742172489</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>3.119514919419175</v>
+        <v>4.6643452911167</v>
       </c>
       <c r="M37" s="13" t="n">
         <v>0.3885830862529954</v>
@@ -3297,7 +3297,7 @@
         <v>119.8811171912314</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>2.446432969378542</v>
+        <v>4.566783978548683</v>
       </c>
       <c r="M38" s="13" t="n">
         <v>0.3857084525741992</v>
@@ -3370,7 +3370,7 @@
         <v>140.6658608471121</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>2.068389163590778</v>
+        <v>4.850479324653034</v>
       </c>
       <c r="M39" s="13" t="n">
         <v>0.3730655920243626</v>
@@ -3443,7 +3443,7 @@
         <v>46.74204581369285</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>15.4186046511628</v>
+        <v>10.48530721282279</v>
       </c>
       <c r="M40" s="13" t="n">
         <v>0.3710100673035752</v>
@@ -3516,7 +3516,7 @@
         <v>141.6910778899985</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>4.711300035423305</v>
+        <v>4.785537043601562</v>
       </c>
       <c r="M41" s="13" t="n">
         <v>0.3698869030583597</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="K42" s="12" t="n"/>
       <c r="L42" s="12" t="n">
-        <v>15.48410938654841</v>
+        <v>7.610192837465557</v>
       </c>
       <c r="M42" s="13" t="n">
         <v>0.3639553354632621</v>
@@ -3656,7 +3656,7 @@
         <v>140.5951198790524</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>3.635978537136397</v>
+        <v>4.962459778333939</v>
       </c>
       <c r="M43" s="13" t="n">
         <v>0.3622293530084952</v>
@@ -3729,7 +3729,7 @@
         <v>22.77494878097579</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>3.668122270742358</v>
+        <v>4.858657243816245</v>
       </c>
       <c r="M44" s="13" t="n">
         <v>0.3620558817440068</v>
@@ -3802,7 +3802,7 @@
         <v>127.3107960015248</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>3.604587657018032</v>
+        <v>5.380525355130539</v>
       </c>
       <c r="M45" s="13" t="n">
         <v>0.3601053144980557</v>
@@ -3875,7 +3875,7 @@
         <v>14.14645821145599</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>3.368421052631576</v>
+        <v>4.616477272727271</v>
       </c>
       <c r="M46" s="13" t="n">
         <v>0.3575031015286503</v>
@@ -3948,7 +3948,7 @@
         <v>121.7488324101623</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>3.63117095063239</v>
+        <v>4.958677685950419</v>
       </c>
       <c r="M47" s="13" t="n">
         <v>0.3401331350142436</v>
@@ -4021,7 +4021,7 @@
         <v>123.5265635387928</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>2.877927891917809</v>
+        <v>4.677078249552635</v>
       </c>
       <c r="M48" s="13" t="n">
         <v>0.3397174684927071</v>
@@ -4094,7 +4094,7 @@
         <v>123.6528213824856</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>3.245972589564805</v>
+        <v>4.774298495323293</v>
       </c>
       <c r="M49" s="13" t="n">
         <v>0.323629528377079</v>
@@ -4167,7 +4167,7 @@
         <v>119.7559141174459</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2.97879362983744</v>
+        <v>4.6189957247045</v>
       </c>
       <c r="M50" s="13" t="n">
         <v>0.3207438177186693</v>
@@ -4240,7 +4240,7 @@
         <v>161.115026559541</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>11.71939652428544</v>
+        <v>9.955516571643376</v>
       </c>
       <c r="M51" s="13" t="n">
         <v>0.3074805777916961</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="K52" s="12" t="n"/>
       <c r="L52" s="12" t="n">
-        <v>10.7898658718331</v>
+        <v>8.875219683655544</v>
       </c>
       <c r="M52" s="13" t="n">
         <v>0.3005133985017966</v>
@@ -4380,7 +4380,7 @@
         <v>141.1581140258447</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>4.772004241781547</v>
+        <v>6.236559139784936</v>
       </c>
       <c r="M53" s="13" t="n">
         <v>0.2897020491539651</v>
@@ -4453,7 +4453,7 @@
         <v>120.6765649492992</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>3.329496876027616</v>
+        <v>4.602197070572567</v>
       </c>
       <c r="M54" s="13" t="n">
         <v>0.2785542604420933</v>
@@ -4526,7 +4526,7 @@
         <v>152.4020167860702</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>10.9691011235955</v>
+        <v>6.432275880649296</v>
       </c>
       <c r="M55" s="13" t="n">
         <v>0.2512723316261195</v>
@@ -4599,7 +4599,7 @@
         <v>64.13399821895985</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2.722694365753853</v>
+        <v>1.540136901057854</v>
       </c>
       <c r="M56" s="13" t="n">
         <v>0.2382752830340032</v>
@@ -4672,7 +4672,7 @@
         <v>150.5243792360934</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>10.74474133030132</v>
+        <v>6.681270536692208</v>
       </c>
       <c r="M57" s="13" t="n">
         <v>0.2264756191470892</v>
@@ -4745,7 +4745,7 @@
         <v>114.7906219755248</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>11.82317304051494</v>
+        <v>8.009509006125981</v>
       </c>
       <c r="M58" s="13" t="n">
         <v>0.2195058768040626</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="K59" s="12" t="n"/>
       <c r="L59" s="12" t="n">
-        <v>12.87501271229532</v>
+        <v>7.55887198371934</v>
       </c>
       <c r="M59" s="13" t="n">
         <v>0.2180765993757863</v>
@@ -4885,7 +4885,7 @@
         <v>30.76413288208192</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>14.45354218583126</v>
+        <v>4.79139504563233</v>
       </c>
       <c r="M60" s="13" t="n">
         <v>0.2098023571281319</v>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="K61" s="12" t="n"/>
       <c r="L61" s="12" t="n">
-        <v>15.41495480690223</v>
+        <v>9.974945192608843</v>
       </c>
       <c r="M61" s="13" t="n">
         <v>0.2091942829854483</v>
@@ -5025,7 +5025,7 @@
         <v>39.90899502775312</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>11.1556982343499</v>
+        <v>7.642487046632107</v>
       </c>
       <c r="M62" s="13" t="n">
         <v>0.2079814708518931</v>
@@ -5098,7 +5098,7 @@
         <v>149.7303672867718</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>10.48507728470691</v>
+        <v>6.312542837559976</v>
       </c>
       <c r="M63" s="13" t="n">
         <v>0.2069424864759201</v>
@@ -5171,7 +5171,7 @@
         <v>86.4824992119545</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>12.6598303582732</v>
+        <v>3.212711667826484</v>
       </c>
       <c r="M64" s="13" t="n">
         <v>0.2023537292343684</v>
@@ -5244,7 +5244,7 @@
         <v>213.5610241247651</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>13.00946049603682</v>
+        <v>8.493298640090341</v>
       </c>
       <c r="M65" s="13" t="n">
         <v>0.2016914460536324</v>
@@ -5313,7 +5313,7 @@
         <v>95.90348696711568</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>12.61147953350104</v>
+        <v>2.936872909698973</v>
       </c>
       <c r="M66" s="13" t="n">
         <v>0.1931289589506998</v>
@@ -5386,7 +5386,7 @@
         <v>86.85614232849146</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>12.45273506428031</v>
+        <v>3.037302228894778</v>
       </c>
       <c r="M67" s="13" t="n">
         <v>0.1930397734588009</v>
@@ -5459,7 +5459,7 @@
         <v>39.8311002358055</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>11.06941838649154</v>
+        <v>7.636363636363641</v>
       </c>
       <c r="M68" s="13" t="n">
         <v>0.1914465845545051</v>
@@ -5532,7 +5532,7 @@
         <v>87.11382196920727</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>12.09839357429716</v>
+        <v>3.093259464450582</v>
       </c>
       <c r="M69" s="13" t="n">
         <v>0.1852616466175038</v>
@@ -5605,7 +5605,7 @@
         <v>860.7499017406718</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>11.95417755562886</v>
+        <v>2.965918769762088</v>
       </c>
       <c r="M70" s="13" t="n">
         <v>0.1828022459972292</v>
@@ -5678,7 +5678,7 @@
         <v>86.66560787154332</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>12.62772801816576</v>
+        <v>3.190013869625519</v>
       </c>
       <c r="M71" s="13" t="n">
         <v>0.1657634698136505</v>
@@ -5751,7 +5751,7 @@
         <v>688.0979293065751</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>16.53709337325158</v>
+        <v>10.8370839839564</v>
       </c>
       <c r="M72" s="13" t="n">
         <v>0.1653594897015658</v>
@@ -5824,7 +5824,7 @@
         <v>70.22875272047494</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>13.60554699537751</v>
+        <v>10.67247072951065</v>
       </c>
       <c r="M73" s="13" t="n">
         <v>0.164500870770665</v>
@@ -5897,7 +5897,7 @@
         <v>68.26956424915849</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>16.65854054932554</v>
+        <v>10.48176081268277</v>
       </c>
       <c r="M74" s="13" t="n">
         <v>0.1632330885320655</v>
@@ -5970,7 +5970,7 @@
         <v>14.05454109693392</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3.606789250353604</v>
+        <v>4.867573371510381</v>
       </c>
       <c r="M75" s="13" t="n">
         <v>0.1621927538534075</v>
@@ -6043,7 +6043,7 @@
         <v>714.494528651919</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>16.93870882412436</v>
+        <v>10.64114832535885</v>
       </c>
       <c r="M76" s="13" t="n">
         <v>0.1498924838633819</v>
@@ -6116,7 +6116,7 @@
         <v>70.49199410693396</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>16.22173366834172</v>
+        <v>10.36385326573219</v>
       </c>
       <c r="M77" s="13" t="n">
         <v>0.1426229043616453</v>
@@ -6189,7 +6189,7 @@
         <v>721.1573306115982</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>16.21414327350821</v>
+        <v>10.39869433434366</v>
       </c>
       <c r="M78" s="13" t="n">
         <v>0.1392484651438273</v>
@@ -6262,7 +6262,7 @@
         <v>49.8766715971249</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>12.75049548557588</v>
+        <v>3.2258064516129</v>
       </c>
       <c r="M79" s="13" t="n">
         <v>0.1225927159311939</v>
@@ -6335,7 +6335,7 @@
         <v>23.32072465206712</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>15.25105584232755</v>
+        <v>10.43165467625899</v>
       </c>
       <c r="M80" s="13" t="n">
         <v>0.1045381050092817</v>
@@ -6408,7 +6408,7 @@
         <v>66.70512660323467</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>15.8845962526944</v>
+        <v>10.16708701134932</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>0.1003681208781735</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="K82" s="12" t="n"/>
       <c r="L82" s="12" t="n">
-        <v>13.22016460905351</v>
+        <v>7.523204689789953</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>0.07706933742746309</v>
@@ -6548,7 +6548,7 @@
         <v>67.10167896997754</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>16.04428288169199</v>
+        <v>9.940513462742651</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>0.07402052484345531</v>
@@ -6621,7 +6621,7 @@
         <v>47.03676922095357</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>14.73486625997185</v>
+        <v>7.970854493265622</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>0.05688149681182586</v>
@@ -6694,7 +6694,7 @@
         <v>21.58387431155958</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>13.62715298885513</v>
+        <v>7.62955854126679</v>
       </c>
       <c r="M85" s="13" t="n">
         <v>0.04315510445165875</v>
@@ -6767,7 +6767,7 @@
         <v>57.90205570746642</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>13.44775556393813</v>
+        <v>8.241857117149532</v>
       </c>
       <c r="M86" s="13" t="n">
         <v>0.02304902388448808</v>
@@ -6840,7 +6840,7 @@
         <v>22.97010995111894</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>1.403508771929829</v>
+        <v>-0.6872852233676952</v>
       </c>
       <c r="M87" s="13" t="n">
         <v>0.01420349970251947</v>
@@ -6913,7 +6913,7 @@
         <v>21.48359089586657</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>13.85634233316353</v>
+        <v>8.232445520581134</v>
       </c>
       <c r="M88" s="13" t="n">
         <v>0.003116098713545318</v>
@@ -6986,7 +6986,7 @@
         <v>192.1245759147101</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>13.07354925775979</v>
+        <v>9.151603973294264</v>
       </c>
       <c r="M89" s="13" t="n">
         <v>-0.001786910548328052</v>
@@ -7059,7 +7059,7 @@
         <v>49.00598236457562</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>14.17322834645669</v>
+        <v>7.384680490901396</v>
       </c>
       <c r="M90" s="13" t="n">
         <v>-0.007593241969580417</v>
@@ -7132,7 +7132,7 @@
         <v>24.43867802596036</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>15.60509554140128</v>
+        <v>8.404436860068266</v>
       </c>
       <c r="M91" s="13" t="n">
         <v>-0.009138331985724779</v>
@@ -7205,7 +7205,7 @@
         <v>10.62708422047197</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>13.46351490236382</v>
+        <v>8.3415112855741</v>
       </c>
       <c r="M92" s="13" t="n">
         <v>-0.01826534030009372</v>
@@ -7278,7 +7278,7 @@
         <v>21.66619963132241</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>13.62260343087789</v>
+        <v>8.11329812770043</v>
       </c>
       <c r="M93" s="13" t="n">
         <v>-0.02418593545401979</v>
@@ -7351,7 +7351,7 @@
         <v>41.84041501059995</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>16.75073002389167</v>
+        <v>11.51115618661258</v>
       </c>
       <c r="M94" s="13" t="n">
         <v>-0.02964210677432155</v>
@@ -7424,7 +7424,7 @@
         <v>219.4369013217262</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>13.61457813280078</v>
+        <v>7.76115162420683</v>
       </c>
       <c r="M95" s="13" t="n">
         <v>-0.03045567769893297</v>
@@ -7497,7 +7497,7 @@
         <v>62.10823553193526</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>13.49304209970055</v>
+        <v>8.085891628921328</v>
       </c>
       <c r="M96" s="13" t="n">
         <v>-0.0308796718727018</v>
@@ -7570,7 +7570,7 @@
         <v>63.26623812687077</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>1.423374980230907</v>
+        <v>1.279216677195194</v>
       </c>
       <c r="M97" s="13" t="n">
         <v>-0.03947134304044445</v>
@@ -7643,7 +7643,7 @@
         <v>16.75926858271935</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>13.17677756033921</v>
+        <v>5.792682926829285</v>
       </c>
       <c r="M98" s="13" t="n">
         <v>-0.05129966804747359</v>
@@ -7716,7 +7716,7 @@
         <v>21.95646244916327</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>12.97861760318249</v>
+        <v>7.524846190250822</v>
       </c>
       <c r="M99" s="13" t="n">
         <v>-0.05132169671618447</v>
@@ -7789,7 +7789,7 @@
         <v>32.99618448866452</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>12.57840871574778</v>
+        <v>8.667941363926079</v>
       </c>
       <c r="M100" s="13" t="n">
         <v>-0.06539170984966339</v>
@@ -7862,7 +7862,7 @@
         <v>9.50858360592842</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>15.4292343387471</v>
+        <v>10.80178173719375</v>
       </c>
       <c r="M101" s="13" t="n">
         <v>-0.07928213233958914</v>
@@ -7935,7 +7935,7 @@
         <v>60.97092407469292</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>12.52467252826126</v>
+        <v>7.656652360515026</v>
       </c>
       <c r="M102" s="13" t="n">
         <v>-0.08945712521079274</v>
@@ -8008,7 +8008,7 @@
         <v>43.55294818508427</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>4.773156899810971</v>
+        <v>2.354570637119124</v>
       </c>
       <c r="M103" s="13" t="n">
         <v>-0.1026829947781038</v>
@@ -8081,7 +8081,7 @@
         <v>947.1637396757613</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>8.585858585858585</v>
+        <v>4.66104002178056</v>
       </c>
       <c r="M104" s="13" t="n">
         <v>-0.110552776153695</v>
@@ -8154,7 +8154,7 @@
         <v>12.93163921575373</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>12.8486897717667</v>
+        <v>7.748184019370452</v>
       </c>
       <c r="M105" s="13" t="n">
         <v>-0.1124227024520604</v>
@@ -8227,7 +8227,7 @@
         <v>40.30169914090978</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>14.4880174291939</v>
+        <v>9.765013054830284</v>
       </c>
       <c r="M106" s="13" t="n">
         <v>-0.1126391059862108</v>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="K107" s="12" t="n"/>
       <c r="L107" s="12" t="n">
-        <v>3.111536620392541</v>
+        <v>4.425514232287564</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>-0.1145340059702797</v>
@@ -8367,7 +8367,7 @@
         <v>94.25412218014009</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>8.46879618051608</v>
+        <v>4.352580927384087</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>-0.140616957786549</v>
@@ -8440,7 +8440,7 @@
         <v>158.834046705842</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>15.03994442514762</v>
+        <v>9.938259310894249</v>
       </c>
       <c r="M109" s="13" t="n">
         <v>-0.1460033796315825</v>
@@ -8513,7 +8513,7 @@
         <v>27.57917204975125</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>12.21374045801527</v>
+        <v>5.356469256884178</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>-0.1478938674825052</v>
@@ -8582,7 +8582,7 @@
         <v>144.7118370249401</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>3.924015529672764</v>
+        <v>5.51136763567257</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>-0.1569908680564051</v>
@@ -8651,7 +8651,7 @@
         <v>30.93116944103448</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>16.15942028985506</v>
+        <v>8.457374830852515</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>-0.1608219913901529</v>
@@ -8724,7 +8724,7 @@
         <v>15.83958952323838</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>14.03872752420467</v>
+        <v>9.786950732356846</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>-0.165445666838018</v>
@@ -8797,7 +8797,7 @@
         <v>42.87877871336121</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>14.65357048048843</v>
+        <v>7.41109176821686</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>-0.1814239107719172</v>
@@ -8866,7 +8866,7 @@
         <v>136.2083029765384</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>0.1457619707018409</v>
+        <v>0.2261123267687903</v>
       </c>
       <c r="M115" s="13" t="n">
         <v>-0.1842021128898192</v>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="K116" s="12" t="n"/>
       <c r="L116" s="12" t="n">
-        <v>3.586206896551714</v>
+        <v>5.167343509312428</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>-0.1847903948715716</v>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="K117" s="12" t="n"/>
       <c r="L117" s="12" t="n">
-        <v>11.76234443998394</v>
+        <v>5.096262740656865</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>-0.1941517079948585</v>
@@ -9073,7 +9073,7 @@
         <v>510.0821204099516</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>18.40550527736598</v>
+        <v>11.1108803986711</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>-0.197887381557229</v>
@@ -9146,7 +9146,7 @@
         <v>14.84503785166933</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>2.261823166552435</v>
+        <v>0.2014775016789816</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>-0.2069899615516914</v>
@@ -9219,7 +9219,7 @@
         <v>148.1123770794378</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>2.151794307713462</v>
+        <v>-0.3420523138832898</v>
       </c>
       <c r="M120" s="13" t="n">
         <v>-0.2405672362663635</v>
@@ -9292,7 +9292,7 @@
         <v>145.7514407219516</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>2.210872455047919</v>
+        <v>-0.5310819091713714</v>
       </c>
       <c r="M121" s="13" t="n">
         <v>-0.2622730971996406</v>
@@ -9365,7 +9365,7 @@
         <v>17.32720858970796</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>15.22157996146436</v>
+        <v>9.190505173463182</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>-0.2713697561958667</v>
@@ -9438,7 +9438,7 @@
         <v>146.8706350291362</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>2.237926972909299</v>
+        <v>0.1085481682496559</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>-0.2765760254823283</v>
@@ -9511,7 +9511,7 @@
         <v>29.61432143223572</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>1.355472721111473</v>
+        <v>0.7070707070707005</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>-0.2766858207886075</v>
@@ -9584,7 +9584,7 @@
         <v>111.4720007382313</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>1.23323431451976</v>
+        <v>0.906235980260206</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>-0.298119783227812</v>
@@ -9657,7 +9657,7 @@
         <v>50.37594248448844</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>13.44168679991213</v>
+        <v>7.358137601330283</v>
       </c>
       <c r="M126" s="13" t="n">
         <v>-0.3020975693708838</v>
@@ -9730,7 +9730,7 @@
         <v>30.50660365017153</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>14.24397370343318</v>
+        <v>7.899275612280099</v>
       </c>
       <c r="M127" s="13" t="n">
         <v>-0.318265570129013</v>
@@ -9803,7 +9803,7 @@
         <v>63.90810846312648</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>1.636506687647521</v>
+        <v>0.7958801498127333</v>
       </c>
       <c r="M128" s="13" t="n">
         <v>-0.3215076685673725</v>
@@ -9876,7 +9876,7 @@
         <v>10.19502768122361</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>13.21776814734561</v>
+        <v>7.289527720739208</v>
       </c>
       <c r="M129" s="13" t="n">
         <v>-0.3279675738295718</v>
@@ -9949,7 +9949,7 @@
         <v>64.11185796320807</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>0.6703039750584505</v>
+        <v>0.4667081518357152</v>
       </c>
       <c r="M130" s="13" t="n">
         <v>-0.3479332638969835</v>
@@ -10022,7 +10022,7 @@
         <v>30.66042805000088</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>13.76811594202898</v>
+        <v>7.534246575342474</v>
       </c>
       <c r="M131" s="13" t="n">
         <v>-0.3499227781373265</v>
@@ -10095,7 +10095,7 @@
         <v>235.5450606971471</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>13.10053902038904</v>
+        <v>8.478690882934735</v>
       </c>
       <c r="M132" s="13" t="n">
         <v>-0.3866464210878825</v>
@@ -10168,7 +10168,7 @@
         <v>60.98250788667318</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>13.49380014587891</v>
+        <v>6.941580756013743</v>
       </c>
       <c r="M133" s="13" t="n">
         <v>-0.3981351203600877</v>
@@ -10241,7 +10241,7 @@
         <v>30.41426825398972</v>
       </c>
       <c r="L134" s="12" t="n">
-        <v>12.08029197080294</v>
+        <v>6.706045865184151</v>
       </c>
       <c r="M134" s="13" t="n">
         <v>-0.4047262337908921</v>
@@ -10314,7 +10314,7 @@
         <v>32.37515248398061</v>
       </c>
       <c r="L135" s="12" t="n">
-        <v>9.3124165554072</v>
+        <v>5.509020618556715</v>
       </c>
       <c r="M135" s="13" t="n">
         <v>-0.405990503833731</v>
@@ -10387,7 +10387,7 @@
         <v>30.39790862118573</v>
       </c>
       <c r="L136" s="12" t="n">
-        <v>13.13389273987595</v>
+        <v>6.746987951807237</v>
       </c>
       <c r="M136" s="13" t="n">
         <v>-0.4209049198323475</v>
@@ -10460,7 +10460,7 @@
         <v>15.71969805522383</v>
       </c>
       <c r="L137" s="12" t="n">
-        <v>12.29909154437456</v>
+        <v>7.348029392117561</v>
       </c>
       <c r="M137" s="13" t="n">
         <v>-0.4236626735595965</v>
@@ -10533,7 +10533,7 @@
         <v>332.6420501814562</v>
       </c>
       <c r="L138" s="12" t="n">
-        <v>9.671965928671277</v>
+        <v>5.885307134561657</v>
       </c>
       <c r="M138" s="13" t="n">
         <v>-0.4304064404715533</v>
@@ -10606,7 +10606,7 @@
         <v>11.6482531917552</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>6.238532110091732</v>
+        <v>4.324324324324325</v>
       </c>
       <c r="M139" s="13" t="n">
         <v>-0.4410827407294621</v>
@@ -10679,7 +10679,7 @@
         <v>29.5513077925793</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>13.47464042392126</v>
+        <v>7.262969588550994</v>
       </c>
       <c r="M140" s="13" t="n">
         <v>-0.4628954396394596</v>
@@ -10752,7 +10752,7 @@
         <v>80.04913248279445</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>9.494351802044122</v>
+        <v>6.27855371361441</v>
       </c>
       <c r="M141" s="13" t="n">
         <v>-0.4777295301232364</v>
@@ -10825,7 +10825,7 @@
         <v>32.28056803012202</v>
       </c>
       <c r="L142" s="12" t="n">
-        <v>9.692513368983956</v>
+        <v>5.973522763965122</v>
       </c>
       <c r="M142" s="13" t="n">
         <v>-0.4815445417338208</v>
@@ -10898,7 +10898,7 @@
         <v>27.13910987939712</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>11.14285714285714</v>
+        <v>5.501743510267354</v>
       </c>
       <c r="M143" s="13" t="n">
         <v>-0.483489652551657</v>
@@ -11044,7 +11044,7 @@
         <v>32.1436012721465</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>18.13953488372096</v>
+        <v>11.78063642518621</v>
       </c>
       <c r="M145" s="13" t="n">
         <v>-0.4885981126231584</v>
@@ -11117,7 +11117,7 @@
         <v>15.9927085040453</v>
       </c>
       <c r="L146" s="12" t="n">
-        <v>10.21798365122615</v>
+        <v>5.890052356020936</v>
       </c>
       <c r="M146" s="13" t="n">
         <v>-0.4895572798683223</v>
@@ -11190,7 +11190,7 @@
         <v>25.98582684886404</v>
       </c>
       <c r="L147" s="12" t="n">
-        <v>2.37354085603112</v>
+        <v>1.270207852193983</v>
       </c>
       <c r="M147" s="13" t="n">
         <v>-0.4912555632760515</v>
@@ -11263,7 +11263,7 @@
         <v>57.24150925353364</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>13.10987703292343</v>
+        <v>5.318559556786706</v>
       </c>
       <c r="M148" s="13" t="n">
         <v>-0.4957841785547426</v>
@@ -11336,7 +11336,7 @@
         <v>270.9594970235516</v>
       </c>
       <c r="L149" s="12" t="n">
-        <v>11.30676931897294</v>
+        <v>5.361088498662636</v>
       </c>
       <c r="M149" s="13" t="n">
         <v>-0.5012552818118569</v>
@@ -11409,7 +11409,7 @@
         <v>29.44179179520683</v>
       </c>
       <c r="L150" s="12" t="n">
-        <v>12.98058622002285</v>
+        <v>6.379928315412187</v>
       </c>
       <c r="M150" s="13" t="n">
         <v>-0.5148374871846436</v>
@@ -11482,7 +11482,7 @@
         <v>29.49908429923411</v>
       </c>
       <c r="L151" s="12" t="n">
-        <v>12.84090909090909</v>
+        <v>6.812477590534227</v>
       </c>
       <c r="M151" s="13" t="n">
         <v>-0.5299013280766971</v>
@@ -11555,7 +11555,7 @@
         <v>29.46779290296077</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>8.719646799117008</v>
+        <v>5.913978494623673</v>
       </c>
       <c r="M152" s="13" t="n">
         <v>-0.5347861039341788</v>
@@ -11628,7 +11628,7 @@
         <v>322.2729937939408</v>
       </c>
       <c r="L153" s="12" t="n">
-        <v>9.700063816209315</v>
+        <v>5.712713619886078</v>
       </c>
       <c r="M153" s="13" t="n">
         <v>-0.5406747293230346</v>
@@ -11701,7 +11701,7 @@
         <v>110.2496453579158</v>
       </c>
       <c r="L154" s="12" t="n">
-        <v>0.4172335600906907</v>
+        <v>0.2807971014492594</v>
       </c>
       <c r="M154" s="13" t="n">
         <v>-0.60396877165862</v>
@@ -11774,7 +11774,7 @@
         <v>11.4114542282776</v>
       </c>
       <c r="L155" s="12" t="n">
-        <v>11.32437619961613</v>
+        <v>7.109879963065557</v>
       </c>
       <c r="M155" s="13" t="n">
         <v>-0.6215509032733989</v>
@@ -11847,7 +11847,7 @@
         <v>23.04547160879889</v>
       </c>
       <c r="L156" s="12" t="n">
-        <v>11.55682903533906</v>
+        <v>6.61798265632132</v>
       </c>
       <c r="M156" s="13" t="n">
         <v>-0.6309920048900377</v>
@@ -11920,7 +11920,7 @@
         <v>38.14708666823284</v>
       </c>
       <c r="L157" s="12" t="n">
-        <v>11.45412579342182</v>
+        <v>6.506754893851663</v>
       </c>
       <c r="M157" s="13" t="n">
         <v>-0.6564014421647248</v>
@@ -11993,7 +11993,7 @@
         <v>36.29005071603961</v>
       </c>
       <c r="L158" s="12" t="n">
-        <v>10.68401937046006</v>
+        <v>6.153846153846154</v>
       </c>
       <c r="M158" s="13" t="n">
         <v>-0.6664887025123778</v>
@@ -12066,7 +12066,7 @@
         <v>29.30430775537931</v>
       </c>
       <c r="L159" s="12" t="n">
-        <v>9.03659447348768</v>
+        <v>5.567606652205348</v>
       </c>
       <c r="M159" s="13" t="n">
         <v>-0.6914948120743744</v>
@@ -12135,7 +12135,7 @@
         <v>27.36121579997873</v>
       </c>
       <c r="L160" s="12" t="n">
-        <v>12.58223684210527</v>
+        <v>5.673485140872248</v>
       </c>
       <c r="M160" s="13" t="n">
         <v>-0.715559944000472</v>
@@ -12208,7 +12208,7 @@
         <v>20.94616021475341</v>
       </c>
       <c r="L161" s="12" t="n">
-        <v>11.50814503415658</v>
+        <v>8.04480651731161</v>
       </c>
       <c r="M161" s="13" t="n">
         <v>-0.7316397846293472</v>
@@ -12281,7 +12281,7 @@
         <v>11.13050532143652</v>
       </c>
       <c r="L162" s="12" t="n">
-        <v>10.76011846001974</v>
+        <v>5.849056603773595</v>
       </c>
       <c r="M162" s="13" t="n">
         <v>-0.7394259454055629</v>
@@ -12354,7 +12354,7 @@
         <v>20.32874778817504</v>
       </c>
       <c r="L163" s="12" t="n">
-        <v>9.749600426212046</v>
+        <v>7.571801566579639</v>
       </c>
       <c r="M163" s="13" t="n">
         <v>-0.7559877477605004</v>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="K164" s="12" t="n"/>
       <c r="L164" s="12" t="n">
-        <v>13.68958644743397</v>
+        <v>8.383802398764995</v>
       </c>
       <c r="M164" s="13" t="n">
         <v>-0.7888748183493445</v>
@@ -12494,7 +12494,7 @@
         <v>25.97967871274014</v>
       </c>
       <c r="L165" s="12" t="n">
-        <v>10.23354564755838</v>
+        <v>5.571370475803183</v>
       </c>
       <c r="M165" s="13" t="n">
         <v>-0.7995063224555911</v>
@@ -12567,7 +12567,7 @@
         <v>576.7771543839037</v>
       </c>
       <c r="L166" s="12" t="n">
-        <v>12.30194436837369</v>
+        <v>5.383824663166781</v>
       </c>
       <c r="M166" s="13" t="n">
         <v>-0.8362019814742263</v>
@@ -12640,7 +12640,7 @@
         <v>58.79317470771069</v>
       </c>
       <c r="L167" s="12" t="n">
-        <v>12.08749040675365</v>
+        <v>5.356176735798024</v>
       </c>
       <c r="M167" s="13" t="n">
         <v>-0.8383559690779583</v>
@@ -12713,7 +12713,7 @@
         <v>25.33077603206454</v>
       </c>
       <c r="L168" s="12" t="n">
-        <v>10.32229965156792</v>
+        <v>5.673758865248235</v>
       </c>
       <c r="M168" s="13" t="n">
         <v>-0.846088757308507</v>
@@ -12786,7 +12786,7 @@
         <v>58.27721320079635</v>
       </c>
       <c r="L169" s="12" t="n">
-        <v>12.22394420767145</v>
+        <v>5.327272727272736</v>
       </c>
       <c r="M169" s="13" t="n">
         <v>-0.8487144004722795</v>
@@ -12859,7 +12859,7 @@
         <v>57.176176882549</v>
       </c>
       <c r="L170" s="12" t="n">
-        <v>11.76702085792993</v>
+        <v>5.049010541890131</v>
       </c>
       <c r="M170" s="13" t="n">
         <v>-0.8513212112733979</v>
@@ -12932,7 +12932,7 @@
         <v>217.8016443112231</v>
       </c>
       <c r="L171" s="12" t="n">
-        <v>12.56242992559373</v>
+        <v>7.521176126959417</v>
       </c>
       <c r="M171" s="13" t="n">
         <v>-0.8550575453542701</v>
@@ -13005,7 +13005,7 @@
         <v>583.884419168701</v>
       </c>
       <c r="L172" s="12" t="n">
-        <v>12.33038462282958</v>
+        <v>5.212488215244027</v>
       </c>
       <c r="M172" s="13" t="n">
         <v>-0.8593605027474892</v>
@@ -13078,7 +13078,7 @@
         <v>58.0506986886069</v>
       </c>
       <c r="L173" s="12" t="n">
-        <v>12.10178710178711</v>
+        <v>5.310218978102199</v>
       </c>
       <c r="M173" s="13" t="n">
         <v>-0.8618179486585329</v>
@@ -13151,7 +13151,7 @@
         <v>586.4353413118401</v>
       </c>
       <c r="L174" s="12" t="n">
-        <v>11.89287771165293</v>
+        <v>5.342587070071758</v>
       </c>
       <c r="M174" s="13" t="n">
         <v>-0.8643712544160712</v>
@@ -13224,7 +13224,7 @@
         <v>57.97167126745606</v>
       </c>
       <c r="L175" s="12" t="n">
-        <v>12.11059190031152</v>
+        <v>5.034658883619114</v>
       </c>
       <c r="M175" s="13" t="n">
         <v>-0.8735514110607212</v>
@@ -13297,7 +13297,7 @@
         <v>581.9136135999951</v>
       </c>
       <c r="L176" s="12" t="n">
-        <v>12.07715421149558</v>
+        <v>5.271303714493802</v>
       </c>
       <c r="M176" s="13" t="n">
         <v>-0.8791164937867565</v>
@@ -13370,7 +13370,7 @@
         <v>11.02558556159753</v>
       </c>
       <c r="L177" s="12" t="n">
-        <v>14.30041152263373</v>
+        <v>8.390243902439011</v>
       </c>
       <c r="M177" s="13" t="n">
         <v>-0.8871476368033813</v>
@@ -13443,7 +13443,7 @@
         <v>58.14840093033335</v>
       </c>
       <c r="L178" s="12" t="n">
-        <v>11.50135082979544</v>
+        <v>5.322639445862198</v>
       </c>
       <c r="M178" s="13" t="n">
         <v>-0.8897467157977095</v>
@@ -13516,7 +13516,7 @@
         <v>27.66016761569319</v>
       </c>
       <c r="L179" s="12" t="n">
-        <v>12.30580539656581</v>
+        <v>6.266924564796894</v>
       </c>
       <c r="M179" s="13" t="n">
         <v>-0.8973296492064189</v>
@@ -13589,7 +13589,7 @@
         <v>42.89230608486336</v>
       </c>
       <c r="L180" s="12" t="n">
-        <v>13.05031446540881</v>
+        <v>7.634730538922163</v>
       </c>
       <c r="M180" s="13" t="n">
         <v>-0.906974506965682</v>
@@ -13662,7 +13662,7 @@
         <v>1392.438301624289</v>
       </c>
       <c r="L181" s="12" t="n">
-        <v>1.584509591024252</v>
+        <v>1.11461755720792</v>
       </c>
       <c r="M181" s="13" t="n">
         <v>-0.9126013945623586</v>
@@ -13735,7 +13735,7 @@
         <v>57.56410393230706</v>
       </c>
       <c r="L182" s="12" t="n">
-        <v>11.86705767350928</v>
+        <v>4.990825688073386</v>
       </c>
       <c r="M182" s="13" t="n">
         <v>-0.9150469450049463</v>
@@ -13808,7 +13808,7 @@
         <v>274.6532108324299</v>
       </c>
       <c r="L183" s="12" t="n">
-        <v>10.04803843074458</v>
+        <v>5.714505460698338</v>
       </c>
       <c r="M183" s="13" t="n">
         <v>-0.9174306152029817</v>
@@ -13881,7 +13881,7 @@
         <v>281.2702812261618</v>
       </c>
       <c r="L184" s="12" t="n">
-        <v>12.6689732861281</v>
+        <v>4.500167916713305</v>
       </c>
       <c r="M184" s="13" t="n">
         <v>-0.9297146691017901</v>
@@ -13954,7 +13954,7 @@
         <v>20.3846275750248</v>
       </c>
       <c r="L185" s="12" t="n">
-        <v>10.14570966001078</v>
+        <v>5.206185567010313</v>
       </c>
       <c r="M185" s="13" t="n">
         <v>-0.9347572368998378</v>
@@ -14027,7 +14027,7 @@
         <v>10.29791764768249</v>
       </c>
       <c r="L186" s="12" t="n">
-        <v>7.507820646506791</v>
+        <v>4.352226720647767</v>
       </c>
       <c r="M186" s="13" t="n">
         <v>-0.937803943098402</v>
@@ -14100,7 +14100,7 @@
         <v>270.3188622827005</v>
       </c>
       <c r="L187" s="12" t="n">
-        <v>8.74913445480836</v>
+        <v>5.325653871947611</v>
       </c>
       <c r="M187" s="13" t="n">
         <v>-0.9623276004656383</v>
@@ -14173,7 +14173,7 @@
         <v>78.85684666282208</v>
       </c>
       <c r="L188" s="12" t="n">
-        <v>21.10289587184226</v>
+        <v>13.64556230124312</v>
       </c>
       <c r="M188" s="13" t="n">
         <v>-0.9679982049276539</v>
@@ -14246,7 +14246,7 @@
         <v>10.51927259847361</v>
       </c>
       <c r="L189" s="12" t="n">
-        <v>10.15706806282721</v>
+        <v>5.728643216080398</v>
       </c>
       <c r="M189" s="13" t="n">
         <v>-0.9715375593141129</v>
@@ -14319,7 +14319,7 @@
         <v>266.5564266432809</v>
       </c>
       <c r="L190" s="12" t="n">
-        <v>9.958352232897628</v>
+        <v>5.461736207237511</v>
       </c>
       <c r="M190" s="13" t="n">
         <v>-0.9767272138801326</v>
@@ -14392,7 +14392,7 @@
         <v>28.0505585793335</v>
       </c>
       <c r="L191" s="12" t="n">
-        <v>9.640905542544886</v>
+        <v>5.840241145440839</v>
       </c>
       <c r="M191" s="13" t="n">
         <v>-0.9917786115000902</v>
@@ -14465,7 +14465,7 @@
         <v>8.825529954237734</v>
       </c>
       <c r="L192" s="12" t="n">
-        <v>21.01648351648351</v>
+        <v>13.82428940568476</v>
       </c>
       <c r="M192" s="13" t="n">
         <v>-0.998595648379085</v>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="K193" s="12" t="n"/>
       <c r="L193" s="12" t="n">
-        <v>11.85626441199077</v>
+        <v>5.167118337850041</v>
       </c>
       <c r="M193" s="13" t="n">
         <v>-1.005199486183527</v>
@@ -14605,7 +14605,7 @@
         <v>20.68748008155402</v>
       </c>
       <c r="L194" s="12" t="n">
-        <v>11.47105682421667</v>
+        <v>7.475678443420364</v>
       </c>
       <c r="M194" s="13" t="n">
         <v>-1.01012755326029</v>
@@ -14678,7 +14678,7 @@
         <v>1269.750695805121</v>
       </c>
       <c r="L195" s="12" t="n">
-        <v>1.950391353557257</v>
+        <v>1.265933021930166</v>
       </c>
       <c r="M195" s="13" t="n">
         <v>-1.01337408511761</v>
@@ -14751,7 +14751,7 @@
         <v>27.67013017708957</v>
       </c>
       <c r="L196" s="12" t="n">
-        <v>11.75993511759934</v>
+        <v>6.573859242072699</v>
       </c>
       <c r="M196" s="13" t="n">
         <v>-1.019143103998351</v>
@@ -14824,7 +14824,7 @@
         <v>1559.793698938395</v>
       </c>
       <c r="L197" s="12" t="n">
-        <v>1.613604958997872</v>
+        <v>0.7322707633221404</v>
       </c>
       <c r="M197" s="13" t="n">
         <v>-1.030729196436476</v>
@@ -14897,7 +14897,7 @@
         <v>26.86961196545344</v>
       </c>
       <c r="L198" s="12" t="n">
-        <v>7.854251012145763</v>
+        <v>2.857142857142869</v>
       </c>
       <c r="M198" s="13" t="n">
         <v>-1.044143206106205</v>
@@ -14970,7 +14970,7 @@
         <v>27.44264780902792</v>
       </c>
       <c r="L199" s="12" t="n">
-        <v>11.64889253486465</v>
+        <v>5.790905557714732</v>
       </c>
       <c r="M199" s="13" t="n">
         <v>-1.054927724546488</v>
@@ -15043,7 +15043,7 @@
         <v>57.11019449060819</v>
       </c>
       <c r="L200" s="12" t="n">
-        <v>10.66077602766038</v>
+        <v>6.271905552481094</v>
       </c>
       <c r="M200" s="13" t="n">
         <v>-1.055669724233847</v>
@@ -15116,7 +15116,7 @@
         <v>277.5376219867976</v>
       </c>
       <c r="L201" s="12" t="n">
-        <v>12.11059982896934</v>
+        <v>6.874999999999987</v>
       </c>
       <c r="M201" s="13" t="n">
         <v>-1.058382039458538</v>
@@ -15189,7 +15189,7 @@
         <v>255.438085386904</v>
       </c>
       <c r="L202" s="12" t="n">
-        <v>9.344304669998271</v>
+        <v>4.694138514210278</v>
       </c>
       <c r="M202" s="13" t="n">
         <v>-1.072267400355263</v>
@@ -15262,7 +15262,7 @@
         <v>148.092693631228</v>
       </c>
       <c r="L203" s="12" t="n">
-        <v>9.64632609179208</v>
+        <v>5.357651752636072</v>
       </c>
       <c r="M203" s="13" t="n">
         <v>-1.07239851508014</v>
@@ -15335,7 +15335,7 @@
         <v>251.4021282810748</v>
       </c>
       <c r="L204" s="12" t="n">
-        <v>8.772465538300466</v>
+        <v>3.796361819922578</v>
       </c>
       <c r="M204" s="13" t="n">
         <v>-1.082950682092196</v>
@@ -15408,7 +15408,7 @@
         <v>20.82831730204153</v>
       </c>
       <c r="L205" s="12" t="n">
-        <v>9.619450317124723</v>
+        <v>5.332656170644978</v>
       </c>
       <c r="M205" s="13" t="n">
         <v>-1.083309817822045</v>
@@ -15481,7 +15481,7 @@
         <v>24.742468549167</v>
       </c>
       <c r="L206" s="12" t="n">
-        <v>8.15602836879432</v>
+        <v>4.362703165098369</v>
       </c>
       <c r="M206" s="13" t="n">
         <v>-1.10706038397033</v>
@@ -15550,7 +15550,7 @@
         <v>41.69712808976456</v>
       </c>
       <c r="L207" s="12" t="n">
-        <v>9.95773903856314</v>
+        <v>5.472510767671657</v>
       </c>
       <c r="M207" s="13" t="n">
         <v>-1.11244050239199</v>
@@ -15623,7 +15623,7 @@
         <v>10.07082786694145</v>
       </c>
       <c r="L208" s="12" t="n">
-        <v>9.170305676855882</v>
+        <v>4.602510460251041</v>
       </c>
       <c r="M208" s="13" t="n">
         <v>-1.140080308401666</v>
@@ -15696,7 +15696,7 @@
         <v>273.618699565151</v>
       </c>
       <c r="L209" s="12" t="n">
-        <v>9.239479601670419</v>
+        <v>4.767589632995728</v>
       </c>
       <c r="M209" s="13" t="n">
         <v>-1.149688864595458</v>
@@ -15769,7 +15769,7 @@
         <v>118.0380085051994</v>
       </c>
       <c r="L210" s="12" t="n">
-        <v>10.72901049475263</v>
+        <v>5.944055944055937</v>
       </c>
       <c r="M210" s="13" t="n">
         <v>-1.15007132419866</v>
@@ -15842,7 +15842,7 @@
         <v>80.38394400961461</v>
       </c>
       <c r="L211" s="12" t="n">
-        <v>9.279778393351812</v>
+        <v>4.669673653489004</v>
       </c>
       <c r="M211" s="13" t="n">
         <v>-1.155954528258872</v>
@@ -15911,7 +15911,7 @@
         <v>2799.517869146028</v>
       </c>
       <c r="L212" s="12" t="n">
-        <v>8.381809997259971</v>
+        <v>4.091357142857155</v>
       </c>
       <c r="M212" s="13" t="n">
         <v>-1.156411614753749</v>
@@ -15984,7 +15984,7 @@
         <v>1308.016519346444</v>
       </c>
       <c r="L213" s="12" t="n">
-        <v>1.589364559854256</v>
+        <v>1.124139501178645</v>
       </c>
       <c r="M213" s="13" t="n">
         <v>-1.159707595061679</v>
@@ -16057,7 +16057,7 @@
         <v>28.69100868551509</v>
       </c>
       <c r="L214" s="12" t="n">
-        <v>1.620288834096506</v>
+        <v>0.7684247293049395</v>
       </c>
       <c r="M214" s="13" t="n">
         <v>-1.163690192850439</v>
@@ -16130,7 +16130,7 @@
         <v>265.3777934036606</v>
       </c>
       <c r="L215" s="12" t="n">
-        <v>9.072088112293496</v>
+        <v>4.577394894596853</v>
       </c>
       <c r="M215" s="13" t="n">
         <v>-1.166031600148966</v>
@@ -16203,7 +16203,7 @@
         <v>275.09498504042</v>
       </c>
       <c r="L216" s="12" t="n">
-        <v>8.833147232413484</v>
+        <v>4.515165441176472</v>
       </c>
       <c r="M216" s="13" t="n">
         <v>-1.171851530755821</v>
@@ -16276,7 +16276,7 @@
         <v>265.7875500011189</v>
       </c>
       <c r="L217" s="12" t="n">
-        <v>8.206224561114993</v>
+        <v>4.523431294678315</v>
       </c>
       <c r="M217" s="13" t="n">
         <v>-1.185095222353581</v>
@@ -16349,7 +16349,7 @@
         <v>893.9218191018064</v>
       </c>
       <c r="L218" s="12" t="n">
-        <v>8.889932985484306</v>
+        <v>3.597223856016929</v>
       </c>
       <c r="M218" s="13" t="n">
         <v>-1.188959299968663</v>
@@ -16422,7 +16422,7 @@
         <v>270.2928003970207</v>
       </c>
       <c r="L219" s="12" t="n">
-        <v>9.503575076608772</v>
+        <v>4.838835862932256</v>
       </c>
       <c r="M219" s="13" t="n">
         <v>-1.1934136180092</v>
@@ -16495,7 +16495,7 @@
         <v>270.835892273964</v>
       </c>
       <c r="L220" s="12" t="n">
-        <v>8.957767049373189</v>
+        <v>4.766920226253157</v>
       </c>
       <c r="M220" s="13" t="n">
         <v>-1.19548091785882</v>
@@ -16568,7 +16568,7 @@
         <v>133.1491558935665</v>
       </c>
       <c r="L221" s="12" t="n">
-        <v>8.607760026084122</v>
+        <v>5.353048153712359</v>
       </c>
       <c r="M221" s="13" t="n">
         <v>-1.197594519023383</v>
@@ -16641,7 +16641,7 @@
         <v>276.7199914207307</v>
       </c>
       <c r="L222" s="12" t="n">
-        <v>8.876279660344411</v>
+        <v>4.473804447151997</v>
       </c>
       <c r="M222" s="13" t="n">
         <v>-1.205535787580837</v>
@@ -16714,7 +16714,7 @@
         <v>126.9098718675785</v>
       </c>
       <c r="L223" s="12" t="n">
-        <v>10.6364428945074</v>
+        <v>6.192468619246871</v>
       </c>
       <c r="M223" s="13" t="n">
         <v>-1.21367403961001</v>
@@ -16787,7 +16787,7 @@
         <v>117.4451545265805</v>
       </c>
       <c r="L224" s="12" t="n">
-        <v>9.701632576468388</v>
+        <v>5.762098597919496</v>
       </c>
       <c r="M224" s="13" t="n">
         <v>-1.220463857211344</v>
@@ -16860,7 +16860,7 @@
         <v>278.0755861169304</v>
       </c>
       <c r="L225" s="12" t="n">
-        <v>8.850220959595955</v>
+        <v>4.472468378398853</v>
       </c>
       <c r="M225" s="13" t="n">
         <v>-1.220620674832896</v>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="K226" s="12" t="n"/>
       <c r="L226" s="12" t="n">
-        <v>8.934460407111189</v>
+        <v>3.897324656543755</v>
       </c>
       <c r="M226" s="13" t="n">
         <v>-1.222941888954679</v>
@@ -17000,7 +17000,7 @@
         <v>204.0175017498489</v>
       </c>
       <c r="L227" s="12" t="n">
-        <v>8.48361967772917</v>
+        <v>4.405874499332429</v>
       </c>
       <c r="M227" s="13" t="n">
         <v>-1.223271945781832</v>
@@ -17073,7 +17073,7 @@
         <v>28.60435304304229</v>
       </c>
       <c r="L228" s="12" t="n">
-        <v>9.19584455559832</v>
+        <v>4.607445632141549</v>
       </c>
       <c r="M228" s="13" t="n">
         <v>-1.225324359934685</v>
@@ -17146,7 +17146,7 @@
         <v>76.96100038615005</v>
       </c>
       <c r="L229" s="12" t="n">
-        <v>15.27863777089784</v>
+        <v>6.874282433983914</v>
       </c>
       <c r="M229" s="13" t="n">
         <v>-1.229672976427438</v>
@@ -17219,7 +17219,7 @@
         <v>14.76748349818401</v>
       </c>
       <c r="L230" s="12" t="n">
-        <v>8.35777126099706</v>
+        <v>5.195729537366534</v>
       </c>
       <c r="M230" s="13" t="n">
         <v>-1.231436199284082</v>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="K231" s="12" t="n"/>
       <c r="L231" s="12" t="n">
-        <v>8.707819597663846</v>
+        <v>4.336486433882203</v>
       </c>
       <c r="M231" s="13" t="n">
         <v>-1.233633443339155</v>
@@ -17359,7 +17359,7 @@
         <v>14.42500440626251</v>
       </c>
       <c r="L232" s="12" t="n">
-        <v>8.496240601503757</v>
+        <v>5.405405405405417</v>
       </c>
       <c r="M232" s="13" t="n">
         <v>-1.23758803301657</v>
@@ -17432,7 +17432,7 @@
         <v>262.8853800806994</v>
       </c>
       <c r="L233" s="12" t="n">
-        <v>8.882389805723845</v>
+        <v>4.373423044575286</v>
       </c>
       <c r="M233" s="13" t="n">
         <v>-1.24613327399744</v>
@@ -17505,7 +17505,7 @@
         <v>81.6134332270376</v>
       </c>
       <c r="L234" s="12" t="n">
-        <v>8.946940985381691</v>
+        <v>4.532467532467521</v>
       </c>
       <c r="M234" s="13" t="n">
         <v>-1.247744380054149</v>
@@ -17578,7 +17578,7 @@
         <v>257.1486369709731</v>
       </c>
       <c r="L235" s="12" t="n">
-        <v>8.833454359061976</v>
+        <v>4.507793273174721</v>
       </c>
       <c r="M235" s="13" t="n">
         <v>-1.248124012487983</v>
@@ -17651,7 +17651,7 @@
         <v>37.08131682275915</v>
       </c>
       <c r="L236" s="12" t="n">
-        <v>6.22273916836289</v>
+        <v>3.719477569562746</v>
       </c>
       <c r="M236" s="13" t="n">
         <v>-1.249618903460468</v>
@@ -17724,7 +17724,7 @@
         <v>9.872313941203942</v>
       </c>
       <c r="L237" s="12" t="n">
-        <v>8.777777777777773</v>
+        <v>4.482390608324449</v>
       </c>
       <c r="M237" s="13" t="n">
         <v>-1.251062006993006</v>
@@ -17797,7 +17797,7 @@
         <v>9.810107769867136</v>
       </c>
       <c r="L238" s="12" t="n">
-        <v>8.754208754208737</v>
+        <v>4.418103448275867</v>
       </c>
       <c r="M238" s="13" t="n">
         <v>-1.277240353715982</v>
@@ -17870,7 +17870,7 @@
         <v>117.5534754505662</v>
       </c>
       <c r="L239" s="12" t="n">
-        <v>10.25448398910696</v>
+        <v>5.841521680338935</v>
       </c>
       <c r="M239" s="13" t="n">
         <v>-1.28467007390233</v>
@@ -17943,7 +17943,7 @@
         <v>79.74042777230454</v>
       </c>
       <c r="L240" s="12" t="n">
-        <v>8.692647871752367</v>
+        <v>4.130808950086062</v>
       </c>
       <c r="M240" s="13" t="n">
         <v>-1.314660259439979</v>
@@ -18016,7 +18016,7 @@
         <v>258.7054075950529</v>
       </c>
       <c r="L241" s="12" t="n">
-        <v>0.3805825242718441</v>
+        <v>-0.08504058755314237</v>
       </c>
       <c r="M241" s="13" t="n">
         <v>-1.321327343558304</v>
@@ -18089,7 +18089,7 @@
         <v>21.90237489926002</v>
       </c>
       <c r="L242" s="12" t="n">
-        <v>7.195662888122234</v>
+        <v>4.017216642754673</v>
       </c>
       <c r="M242" s="13" t="n">
         <v>-1.332724298187971</v>
@@ -18162,7 +18162,7 @@
         <v>29.7157872455073</v>
       </c>
       <c r="L243" s="12" t="n">
-        <v>1.050847457627113</v>
+        <v>0.3365870077414845</v>
       </c>
       <c r="M243" s="13" t="n">
         <v>-1.356563494886715</v>
@@ -18235,7 +18235,7 @@
         <v>31.9023752152123</v>
       </c>
       <c r="L244" s="12" t="n">
-        <v>10.04228329809727</v>
+        <v>4.798657718120802</v>
       </c>
       <c r="M244" s="13" t="n">
         <v>-1.357401403070792</v>
@@ -18304,7 +18304,7 @@
         <v>89.80497203390814</v>
       </c>
       <c r="L245" s="12" t="n">
-        <v>9.12781399926188</v>
+        <v>4.389268063073648</v>
       </c>
       <c r="M245" s="13" t="n">
         <v>-1.363010131487948</v>
@@ -18377,7 +18377,7 @@
         <v>29.15558000146961</v>
       </c>
       <c r="L246" s="12" t="n">
-        <v>1.174033149171261</v>
+        <v>0.6526966678117585</v>
       </c>
       <c r="M246" s="13" t="n">
         <v>-1.370623380253201</v>
@@ -18450,7 +18450,7 @@
         <v>910.2149903890993</v>
       </c>
       <c r="L247" s="12" t="n">
-        <v>9.104613701294761</v>
+        <v>4.27104150206814</v>
       </c>
       <c r="M247" s="13" t="n">
         <v>-1.388989918276284</v>
@@ -18523,7 +18523,7 @@
         <v>82.10955116807759</v>
       </c>
       <c r="L248" s="12" t="n">
-        <v>8.549536227987641</v>
+        <v>4.072689779610772</v>
       </c>
       <c r="M248" s="13" t="n">
         <v>-1.395922282323672</v>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="K249" s="12" t="n"/>
       <c r="L249" s="12" t="n">
-        <v>8.679706601466997</v>
+        <v>4.220398593200492</v>
       </c>
       <c r="M249" s="13" t="n">
         <v>-1.397056698776677</v>
@@ -18663,7 +18663,7 @@
         <v>9.258224671128593</v>
       </c>
       <c r="L250" s="12" t="n">
-        <v>15.43287327478042</v>
+        <v>9.004739336492884</v>
       </c>
       <c r="M250" s="13" t="n">
         <v>-1.403190452023621</v>
@@ -18736,7 +18736,7 @@
         <v>258.5495488517549</v>
       </c>
       <c r="L251" s="12" t="n">
-        <v>1.280846063454755</v>
+        <v>0.4311349335819115</v>
       </c>
       <c r="M251" s="13" t="n">
         <v>-1.412433477738333</v>
@@ -18809,7 +18809,7 @@
         <v>81.62309986062139</v>
       </c>
       <c r="L252" s="12" t="n">
-        <v>8.740359897172256</v>
+        <v>4.160186625194418</v>
       </c>
       <c r="M252" s="13" t="n">
         <v>-1.414675742822821</v>
@@ -18882,7 +18882,7 @@
         <v>9.954022463055175</v>
       </c>
       <c r="L253" s="12" t="n">
-        <v>11.04910714285712</v>
+        <v>7.335490830636449</v>
       </c>
       <c r="M253" s="13" t="n">
         <v>-1.429148294201305</v>
@@ -18955,7 +18955,7 @@
         <v>12.47304596422314</v>
       </c>
       <c r="L254" s="12" t="n">
-        <v>14.52358926919519</v>
+        <v>8.691834942932397</v>
       </c>
       <c r="M254" s="13" t="n">
         <v>-1.429379470401694</v>
@@ -19028,7 +19028,7 @@
         <v>54.05556812040566</v>
       </c>
       <c r="L255" s="12" t="n">
-        <v>9.328128210396546</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M255" s="13" t="n">
         <v>-1.753086711030533</v>
@@ -19101,7 +19101,7 @@
         <v>10.26402862399123</v>
       </c>
       <c r="L256" s="12" t="n">
-        <v>6.8157614483493</v>
+        <v>4.153686396677037</v>
       </c>
       <c r="M256" s="13" t="n">
         <v>-1.773141142951928</v>
@@ -19174,7 +19174,7 @@
         <v>93.0161689632241</v>
       </c>
       <c r="L257" s="12" t="n">
-        <v>7.464103476919437</v>
+        <v>4.742077261161248</v>
       </c>
       <c r="M257" s="13" t="n">
         <v>-1.823072470849977</v>
@@ -19247,7 +19247,7 @@
         <v>481.1344525984621</v>
       </c>
       <c r="L258" s="12" t="n">
-        <v>7.263490629939051</v>
+        <v>5.055173481347164</v>
       </c>
       <c r="M258" s="13" t="n">
         <v>-2.009281665069499</v>
@@ -19320,7 +19320,7 @@
         <v>119.3208453783596</v>
       </c>
       <c r="L259" s="12" t="n">
-        <v>7.138257749977006</v>
+        <v>4.084003574620199</v>
       </c>
       <c r="M259" s="13" t="n">
         <v>-2.029264682835551</v>
@@ -19393,7 +19393,7 @@
         <v>36.37843001498084</v>
       </c>
       <c r="L260" s="12" t="n">
-        <v>10.22655758338578</v>
+        <v>7.190942472460216</v>
       </c>
       <c r="M260" s="13" t="n">
         <v>-2.079804799812567</v>
@@ -19466,7 +19466,7 @@
         <v>86.50281449364495</v>
       </c>
       <c r="L261" s="12" t="n">
-        <v>12.34156104069379</v>
+        <v>6.988564167725531</v>
       </c>
       <c r="M261" s="13" t="n">
         <v>-2.084858870899475</v>
@@ -19539,7 +19539,7 @@
         <v>34.80348739639938</v>
       </c>
       <c r="L262" s="12" t="n">
-        <v>9.393346379647749</v>
+        <v>7.362355953905242</v>
       </c>
       <c r="M262" s="13" t="n">
         <v>-2.116246279845968</v>
@@ -19612,7 +19612,7 @@
         <v>36.42457184000968</v>
       </c>
       <c r="L263" s="12" t="n">
-        <v>9.759149202377237</v>
+        <v>7.374541003671986</v>
       </c>
       <c r="M263" s="13" t="n">
         <v>-2.134963961651281</v>
@@ -19685,7 +19685,7 @@
         <v>361.8304741581376</v>
       </c>
       <c r="L264" s="12" t="n">
-        <v>9.713926438226972</v>
+        <v>7.338377314387645</v>
       </c>
       <c r="M264" s="13" t="n">
         <v>-2.146838839228963</v>
@@ -19758,7 +19758,7 @@
         <v>34.73181865670217</v>
       </c>
       <c r="L265" s="12" t="n">
-        <v>9.747292418772568</v>
+        <v>7.179487179487176</v>
       </c>
       <c r="M265" s="13" t="n">
         <v>-2.151716348701855</v>
@@ -19831,7 +19831,7 @@
         <v>35.7120802307211</v>
       </c>
       <c r="L266" s="12" t="n">
-        <v>9.269841269841272</v>
+        <v>7.361197754210846</v>
       </c>
       <c r="M266" s="13" t="n">
         <v>-2.16857204553494</v>
@@ -19904,7 +19904,7 @@
         <v>36.45859953341175</v>
       </c>
       <c r="L267" s="12" t="n">
-        <v>9.690528290090672</v>
+        <v>7.04697986577183</v>
       </c>
       <c r="M267" s="13" t="n">
         <v>-2.179964791175939</v>
@@ -19977,7 +19977,7 @@
         <v>345.0060068450187</v>
       </c>
       <c r="L268" s="12" t="n">
-        <v>9.765586363786216</v>
+        <v>7.625913234628579</v>
       </c>
       <c r="M268" s="13" t="n">
         <v>-2.183880260411754</v>
@@ -20050,7 +20050,7 @@
         <v>35.05365168857782</v>
       </c>
       <c r="L269" s="12" t="n">
-        <v>9.361839974084862</v>
+        <v>7.242693773824649</v>
       </c>
       <c r="M269" s="13" t="n">
         <v>-2.189471493890019</v>
@@ -20123,7 +20123,7 @@
         <v>364.099161433808</v>
       </c>
       <c r="L270" s="12" t="n">
-        <v>9.34141464633842</v>
+        <v>7.043890503135053</v>
       </c>
       <c r="M270" s="13" t="n">
         <v>-2.200711799854188</v>
@@ -20196,7 +20196,7 @@
         <v>1048.741620976973</v>
       </c>
       <c r="L271" s="12" t="n">
-        <v>0.2291731772682937</v>
+        <v>0.3203761101790548</v>
       </c>
       <c r="M271" s="13" t="n">
         <v>-10.37242228371417</v>
@@ -20269,7 +20269,7 @@
         <v>1027.208597523371</v>
       </c>
       <c r="L272" s="12" t="n">
-        <v>0.2157132078391966</v>
+        <v>0.3059495570508775</v>
       </c>
       <c r="M272" s="13" t="n">
         <v>-12.39135751149893</v>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="K273" s="12" t="n"/>
       <c r="L273" s="12" t="n">
-        <v>6.556654279775764</v>
+        <v>5.408099688473533</v>
       </c>
       <c r="M273" s="13" t="n"/>
       <c r="N273" s="13" t="n"/>
@@ -20401,7 +20401,7 @@
       </c>
       <c r="K274" s="12" t="n"/>
       <c r="L274" s="12" t="n">
-        <v>9.414466130884014</v>
+        <v>7.805429864253388</v>
       </c>
       <c r="M274" s="13" t="n"/>
       <c r="N274" s="13" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="K275" s="12" t="n"/>
       <c r="L275" s="12" t="n">
-        <v>2.596491228070175</v>
+        <v>5.293482175009001</v>
       </c>
       <c r="M275" s="13" t="n"/>
       <c r="N275" s="13" t="n"/>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="K276" s="12" t="n"/>
       <c r="L276" s="12" t="n">
-        <v>10.93544137022397</v>
+        <v>4.726368159203997</v>
       </c>
       <c r="M276" s="13" t="n"/>
       <c r="N276" s="13" t="n"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="K277" s="12" t="n"/>
       <c r="L277" s="12" t="n">
-        <v>7.32362821948489</v>
+        <v>4.378131126116336</v>
       </c>
       <c r="M277" s="13" t="n"/>
       <c r="N277" s="13" t="n"/>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="K278" s="12" t="n"/>
       <c r="L278" s="12" t="n">
-        <v>10.66306381209727</v>
+        <v>8.942091262533269</v>
       </c>
       <c r="M278" s="13" t="n"/>
       <c r="N278" s="13" t="n"/>
@@ -20705,9 +20705,7 @@
         <v>0</v>
       </c>
       <c r="K279" s="12" t="n"/>
-      <c r="L279" s="12" t="n">
-        <v>5.656324582338912</v>
-      </c>
+      <c r="L279" s="12" t="n"/>
       <c r="M279" s="13" t="n"/>
       <c r="N279" s="13" t="n"/>
       <c r="O279" s="13" t="n"/>
@@ -20766,9 +20764,7 @@
         <v>0.1815156557253132</v>
       </c>
       <c r="K280" s="12" t="n"/>
-      <c r="L280" s="12" t="n">
-        <v>3.408289587087676</v>
-      </c>
+      <c r="L280" s="12" t="n"/>
       <c r="M280" s="13" t="n"/>
       <c r="N280" s="13" t="n"/>
       <c r="O280" s="13" t="n"/>
@@ -20828,7 +20824,7 @@
       </c>
       <c r="K281" s="12" t="n"/>
       <c r="L281" s="12" t="n">
-        <v>21.13643982567886</v>
+        <v>15.09794553272814</v>
       </c>
       <c r="M281" s="13" t="n"/>
       <c r="N281" s="13" t="n"/>
@@ -20889,7 +20885,7 @@
       </c>
       <c r="K282" s="12" t="n"/>
       <c r="L282" s="12" t="n">
-        <v>3.577417551704865</v>
+        <v>1.367614879649892</v>
       </c>
       <c r="M282" s="13" t="n"/>
       <c r="N282" s="13" t="n"/>
@@ -20950,7 +20946,7 @@
       </c>
       <c r="K283" s="12" t="n"/>
       <c r="L283" s="12" t="n">
-        <v>15.49019607843139</v>
+        <v>10.29962546816479</v>
       </c>
       <c r="M283" s="13" t="n"/>
       <c r="N283" s="13" t="n"/>
@@ -21010,9 +21006,7 @@
         <v>0</v>
       </c>
       <c r="K284" s="12" t="n"/>
-      <c r="L284" s="12" t="n">
-        <v>12.93333333333335</v>
-      </c>
+      <c r="L284" s="12" t="n"/>
       <c r="M284" s="13" t="n"/>
       <c r="N284" s="13" t="n"/>
       <c r="O284" s="13" t="n"/>
@@ -21072,7 +21066,7 @@
       </c>
       <c r="K285" s="12" t="n"/>
       <c r="L285" s="12" t="n">
-        <v>12.16633375703651</v>
+        <v>7.594495732450812</v>
       </c>
       <c r="M285" s="13" t="n"/>
       <c r="N285" s="13" t="n"/>
@@ -21137,7 +21131,7 @@
         <v>22.40231175706311</v>
       </c>
       <c r="L286" s="17" t="n">
-        <v>8.889891696750896</v>
+        <v>7.627118644067776</v>
       </c>
       <c r="M286" s="18" t="n">
         <v>0.1941506733753158</v>
@@ -21212,7 +21206,7 @@
         <v>230.3530552745098</v>
       </c>
       <c r="L287" s="17" t="n">
-        <v>10.43973144813481</v>
+        <v>8.723627768537145</v>
       </c>
       <c r="M287" s="18" t="n">
         <v>0.1840142778731264</v>
@@ -21287,7 +21281,7 @@
         <v>228.9219592503339</v>
       </c>
       <c r="L288" s="17" t="n">
-        <v>10.60926734813348</v>
+        <v>9.134935797751819</v>
       </c>
       <c r="M288" s="18" t="n">
         <v>0.1822958635431886</v>
@@ -21362,7 +21356,7 @@
         <v>229.4252547664068</v>
       </c>
       <c r="L289" s="17" t="n">
-        <v>10.55339328054401</v>
+        <v>8.073121665354677</v>
       </c>
       <c r="M289" s="18" t="n">
         <v>0.1772674373419185</v>
@@ -21437,7 +21431,7 @@
         <v>222.4733640314144</v>
       </c>
       <c r="L290" s="17" t="n">
-        <v>10.17042583490284</v>
+        <v>7.503698059079289</v>
       </c>
       <c r="M290" s="18" t="n">
         <v>0.1692023488282194</v>
@@ -21512,7 +21506,7 @@
         <v>23.4566490950615</v>
       </c>
       <c r="L291" s="17" t="n">
-        <v>10.11774967291759</v>
+        <v>8.229747106729546</v>
       </c>
       <c r="M291" s="18" t="n">
         <v>0.1680430358042399</v>
@@ -21587,7 +21581,7 @@
         <v>223.0050645185009</v>
       </c>
       <c r="L292" s="17" t="n">
-        <v>9.360502137723991</v>
+        <v>8.150413817920121</v>
       </c>
       <c r="M292" s="18" t="n">
         <v>0.1594459191525645</v>
@@ -21662,7 +21656,7 @@
         <v>220.9240431534428</v>
       </c>
       <c r="L293" s="17" t="n">
-        <v>10.20918178452423</v>
+        <v>7.551260048776087</v>
       </c>
       <c r="M293" s="18" t="n">
         <v>0.1499760706047594</v>
@@ -21737,7 +21731,7 @@
         <v>225.0260199003596</v>
       </c>
       <c r="L294" s="17" t="n">
-        <v>9.420880913539964</v>
+        <v>7.741388541852579</v>
       </c>
       <c r="M294" s="18" t="n">
         <v>0.137919932552608</v>
@@ -21812,7 +21806,7 @@
         <v>230.3450627377987</v>
       </c>
       <c r="L295" s="17" t="n">
-        <v>10.21930213974962</v>
+        <v>7.821253311330167</v>
       </c>
       <c r="M295" s="18" t="n">
         <v>0.123538431628378</v>
@@ -21887,7 +21881,7 @@
         <v>221.4144840009396</v>
       </c>
       <c r="L296" s="17" t="n">
-        <v>9.934936089705126</v>
+        <v>7.49447276993187</v>
       </c>
       <c r="M296" s="18" t="n">
         <v>0.1197309926688758</v>
@@ -21962,7 +21956,7 @@
         <v>231.2153603680001</v>
       </c>
       <c r="L297" s="17" t="n">
-        <v>9.420162143108923</v>
+        <v>7.520457202234065</v>
       </c>
       <c r="M297" s="18" t="n">
         <v>0.1073142582215872</v>
@@ -22037,7 +22031,7 @@
         <v>226.1758045655558</v>
       </c>
       <c r="L298" s="17" t="n">
-        <v>10.01760642860368</v>
+        <v>7.437287836705897</v>
       </c>
       <c r="M298" s="18" t="n">
         <v>0.1000828275172911</v>
@@ -22112,7 +22106,7 @@
         <v>227.2281747114946</v>
       </c>
       <c r="L299" s="17" t="n">
-        <v>10.78582434514639</v>
+        <v>8.182502102048939</v>
       </c>
       <c r="M299" s="18" t="n">
         <v>0.086997766498768</v>
@@ -22187,7 +22181,7 @@
         <v>22.65909280079883</v>
       </c>
       <c r="L300" s="17" t="n">
-        <v>10.46669687358404</v>
+        <v>7.16483516483517</v>
       </c>
       <c r="M300" s="18" t="n">
         <v>0.0811529360087937</v>
@@ -22262,7 +22256,7 @@
         <v>22.46109191082057</v>
       </c>
       <c r="L301" s="17" t="n">
-        <v>10.11850501367364</v>
+        <v>7.857142857142874</v>
       </c>
       <c r="M301" s="18" t="n">
         <v>0.07417002362553926</v>
@@ -22335,7 +22329,7 @@
       </c>
       <c r="K302" s="17" t="n"/>
       <c r="L302" s="17" t="n">
-        <v>10.03541389995572</v>
+        <v>6.838304822487751</v>
       </c>
       <c r="M302" s="18" t="n">
         <v>-0.9886786544280333</v>
@@ -22406,7 +22400,7 @@
         <v>7045.726664889474</v>
       </c>
       <c r="L303" s="17" t="n">
-        <v>4.329501915708822</v>
+        <v>5.420054200542013</v>
       </c>
       <c r="M303" s="18" t="n">
         <v>-1.673476799703988</v>
@@ -22481,7 +22475,7 @@
         <v>24.32921462436839</v>
       </c>
       <c r="L304" s="17" t="n">
-        <v>6.663644605621055</v>
+        <v>3.747795414462085</v>
       </c>
       <c r="M304" s="18" t="n">
         <v>-1.726344789318005</v>
@@ -22556,7 +22550,7 @@
         <v>1273.129090959418</v>
       </c>
       <c r="L305" s="17" t="n">
-        <v>8.582272282076397</v>
+        <v>4.189998825233965</v>
       </c>
       <c r="M305" s="18" t="n">
         <v>-1.751170715497623</v>
@@ -22631,7 +22625,7 @@
         <v>65.56122591083897</v>
       </c>
       <c r="L306" s="17" t="n">
-        <v>10.46182846371348</v>
+        <v>6.352087114337568</v>
       </c>
       <c r="M306" s="18" t="n">
         <v>-1.753372388194087</v>

--- a/momentum/ETFs/etf_rankings.xlsx
+++ b/momentum/ETFs/etf_rankings.xlsx
@@ -861,7 +861,7 @@
         <v>36.0477501703408</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>9.521142537104454</v>
+        <v>11.96679072430575</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>2.587885919481731</v>
@@ -930,7 +930,7 @@
         <v>100.8931125031753</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>22.85285285285286</v>
+        <v>32.23790539812521</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>2.409829391027872</v>
@@ -1003,7 +1003,7 @@
         <v>10.27335657280187</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>12.55992329817834</v>
+        <v>15.66502463054187</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>2.119599627295667</v>
@@ -1076,7 +1076,7 @@
         <v>98.7865593330821</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6.307830066660025</v>
+        <v>7.117794486215523</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>1.964824078457934</v>
@@ -1149,7 +1149,7 @@
         <v>233.9747237878053</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>21.42433736980267</v>
+        <v>30.84223013048635</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>1.809315469142009</v>
@@ -1222,7 +1222,7 @@
         <v>11.51211590841348</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>13.88400702987698</v>
+        <v>19.11764705882353</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>1.499121109419864</v>
@@ -1295,7 +1295,7 @@
         <v>11.52659113059735</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>13.784021071115</v>
+        <v>18.89908256880734</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>1.472132231703636</v>
@@ -1368,7 +1368,7 @@
         <v>36.02111017033209</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>9.31729155008394</v>
+        <v>11.53297173850985</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>1.461747498313979</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n">
-        <v>14.0726933830382</v>
+        <v>19.06614785992218</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>1.434718521984453</v>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n">
-        <v>17.33193277310925</v>
+        <v>24.38752783964364</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>1.426946458032408</v>
@@ -1575,7 +1575,7 @@
         <v>46.50322445222943</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>17.45751489737364</v>
+        <v>24.49122807017543</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>1.114003771915568</v>
@@ -1648,7 +1648,7 @@
         <v>79.55869184947483</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>15.81987659183406</v>
+        <v>19.96192548273048</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.9993359730462348</v>
@@ -1721,7 +1721,7 @@
         <v>31.92340267987092</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>8.298755186722007</v>
+        <v>11.50180742688136</v>
       </c>
       <c r="M16" s="13" t="n">
         <v>0.9838238195907922</v>
@@ -1794,7 +1794,7 @@
         <v>15.06882232720338</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>7.681940700808632</v>
+        <v>11.12656467315716</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.969477771975843</v>
@@ -1867,7 +1867,7 @@
         <v>87.31276210421984</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>15.65414972494617</v>
+        <v>19.0276923076923</v>
       </c>
       <c r="M18" s="13" t="n">
         <v>0.9583815914272557</v>
@@ -1940,7 +1940,7 @@
         <v>10.32081438282395</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>8.712871287128721</v>
+        <v>10.35175879396986</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0.9015270281536603</v>
@@ -2013,7 +2013,7 @@
         <v>96.546041669602</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>8.080488832701228</v>
+        <v>11.65650848933393</v>
       </c>
       <c r="M20" s="13" t="n">
         <v>0.8900905545445528</v>
@@ -2086,7 +2086,7 @@
         <v>119.0376963887748</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>7.397236763065318</v>
+        <v>10.41997529557086</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>0.8418551892331569</v>
@@ -2159,7 +2159,7 @@
         <v>101.232387650885</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>8.608870967741922</v>
+        <v>10.21994884910487</v>
       </c>
       <c r="M22" s="13" t="n">
         <v>0.8092555965181292</v>
@@ -2232,7 +2232,7 @@
         <v>9.563165939602666</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>9.031556039173005</v>
+        <v>13.99317406143346</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0.6982167380038752</v>
@@ -2301,7 +2301,7 @@
         <v>15.79458076819297</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>10.16722408026756</v>
+        <v>15.66011235955056</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>0.5823936403414288</v>
@@ -2370,7 +2370,7 @@
         <v>59.06561704270673</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>11.09942135718043</v>
+        <v>15.45189504373177</v>
       </c>
       <c r="M25" s="13" t="n">
         <v>0.5770735917841835</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K26" s="12" t="n"/>
       <c r="L26" s="12" t="n">
-        <v>10.42780748663101</v>
+        <v>15.60531840447865</v>
       </c>
       <c r="M26" s="13" t="n">
         <v>0.5062801260866725</v>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n">
-        <v>10.31318281136198</v>
+        <v>14.34395289143893</v>
       </c>
       <c r="M27" s="13" t="n">
         <v>0.5005117023119937</v>
@@ -2577,7 +2577,7 @@
         <v>9.118306597702359</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>9.50173812282733</v>
+        <v>16.09336609336607</v>
       </c>
       <c r="M28" s="13" t="n">
         <v>0.4529079872672848</v>
@@ -2646,7 +2646,7 @@
         <v>69.49235500216736</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7.185025197984163</v>
+        <v>10.83978558665872</v>
       </c>
       <c r="M29" s="13" t="n">
         <v>0.4508714834265253</v>
@@ -2719,7 +2719,7 @@
         <v>143.1946106746558</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>5.003523608174776</v>
+        <v>12.62282690854117</v>
       </c>
       <c r="M30" s="13" t="n">
         <v>0.4503353048516891</v>
@@ -2792,7 +2792,7 @@
         <v>144.7312340382067</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>4.862799583188604</v>
+        <v>12.5232948192322</v>
       </c>
       <c r="M31" s="13" t="n">
         <v>0.4259231450785703</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="K32" s="12" t="n"/>
       <c r="L32" s="12" t="n">
-        <v>10.37279675557636</v>
+        <v>14.42432082794307</v>
       </c>
       <c r="M32" s="13" t="n">
         <v>0.4173727600558846</v>
@@ -2932,7 +2932,7 @@
         <v>120.6566699090284</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>5.02416263956007</v>
+        <v>13.32374359435404</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>0.3970893923996646</v>
@@ -3005,7 +3005,7 @@
         <v>13.55309182552233</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>4.992548435171384</v>
+        <v>12.0922832140016</v>
       </c>
       <c r="M34" s="13" t="n">
         <v>0.3955895232520931</v>
@@ -3078,7 +3078,7 @@
         <v>140.3103062758128</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>5.625676163000337</v>
+        <v>13.13248358439552</v>
       </c>
       <c r="M35" s="13" t="n">
         <v>0.3904616228278521</v>
@@ -3151,7 +3151,7 @@
         <v>12583.42464395361</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>4.308748295198472</v>
+        <v>13.5300693051813</v>
       </c>
       <c r="M36" s="13" t="n">
         <v>0.3903525261822038</v>
@@ -3224,7 +3224,7 @@
         <v>123.9928742172489</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>4.6643452911167</v>
+        <v>13.8866860516345</v>
       </c>
       <c r="M37" s="13" t="n">
         <v>0.3885830862529954</v>
@@ -3297,7 +3297,7 @@
         <v>119.8811171912314</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>4.566783978548683</v>
+        <v>12.96279532904863</v>
       </c>
       <c r="M38" s="13" t="n">
         <v>0.3857084525741992</v>
@@ -3370,7 +3370,7 @@
         <v>140.6658608471121</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>4.850479324653034</v>
+        <v>13.25245344254695</v>
       </c>
       <c r="M39" s="13" t="n">
         <v>0.3730655920243626</v>
@@ -3443,7 +3443,7 @@
         <v>46.74204581369285</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>10.48530721282279</v>
+        <v>16.4476771468794</v>
       </c>
       <c r="M40" s="13" t="n">
         <v>0.3710100673035752</v>
@@ -3516,7 +3516,7 @@
         <v>141.6910778899985</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>4.785537043601562</v>
+        <v>12.65243902439026</v>
       </c>
       <c r="M41" s="13" t="n">
         <v>0.3698869030583597</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="K42" s="12" t="n"/>
       <c r="L42" s="12" t="n">
-        <v>7.610192837465557</v>
+        <v>14.63683052090976</v>
       </c>
       <c r="M42" s="13" t="n">
         <v>0.3639553354632621</v>
@@ -3656,7 +3656,7 @@
         <v>140.5951198790524</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>4.962459778333939</v>
+        <v>12.26768642447418</v>
       </c>
       <c r="M43" s="13" t="n">
         <v>0.3622293530084952</v>
@@ -3729,7 +3729,7 @@
         <v>22.77494878097579</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>4.858657243816245</v>
+        <v>12.45855045002369</v>
       </c>
       <c r="M44" s="13" t="n">
         <v>0.3620558817440068</v>
@@ -3802,7 +3802,7 @@
         <v>127.3107960015248</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>5.380525355130539</v>
+        <v>12.71538918597741</v>
       </c>
       <c r="M45" s="13" t="n">
         <v>0.3601053144980557</v>
@@ -3875,7 +3875,7 @@
         <v>14.14645821145599</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>4.616477272727271</v>
+        <v>12.61467889908257</v>
       </c>
       <c r="M46" s="13" t="n">
         <v>0.3575031015286503</v>
@@ -3948,7 +3948,7 @@
         <v>121.7488324101623</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>4.958677685950419</v>
+        <v>11.89427312775331</v>
       </c>
       <c r="M47" s="13" t="n">
         <v>0.3401331350142436</v>
@@ -4021,7 +4021,7 @@
         <v>123.5265635387928</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>4.677078249552635</v>
+        <v>13.16391136123814</v>
       </c>
       <c r="M48" s="13" t="n">
         <v>0.3397174684927071</v>
@@ -4094,7 +4094,7 @@
         <v>123.6528213824856</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>4.774298495323293</v>
+        <v>13.08928101132474</v>
       </c>
       <c r="M49" s="13" t="n">
         <v>0.323629528377079</v>
@@ -4167,7 +4167,7 @@
         <v>119.7559141174459</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>4.6189957247045</v>
+        <v>12.71676300578035</v>
       </c>
       <c r="M50" s="13" t="n">
         <v>0.3207438177186693</v>
@@ -4240,7 +4240,7 @@
         <v>161.115026559541</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>9.955516571643376</v>
+        <v>11.03378463874478</v>
       </c>
       <c r="M51" s="13" t="n">
         <v>0.3074805777916961</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="K52" s="12" t="n"/>
       <c r="L52" s="12" t="n">
-        <v>8.875219683655544</v>
+        <v>11.78947368421053</v>
       </c>
       <c r="M52" s="13" t="n">
         <v>0.3005133985017966</v>
@@ -4380,7 +4380,7 @@
         <v>141.1581140258447</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>6.236559139784936</v>
+        <v>13.65030674846624</v>
       </c>
       <c r="M53" s="13" t="n">
         <v>0.2897020491539651</v>
@@ -4453,7 +4453,7 @@
         <v>120.6765649492992</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>4.602197070572567</v>
+        <v>13.98385780357305</v>
       </c>
       <c r="M54" s="13" t="n">
         <v>0.2785542604420933</v>
@@ -4526,7 +4526,7 @@
         <v>152.4020167860702</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>6.432275880649296</v>
+        <v>10.7979245547609</v>
       </c>
       <c r="M55" s="13" t="n">
         <v>0.2512723316261195</v>
@@ -4599,7 +4599,7 @@
         <v>64.13399821895985</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>1.540136901057854</v>
+        <v>1.052794550239966</v>
       </c>
       <c r="M56" s="13" t="n">
         <v>0.2382752830340032</v>
@@ -4672,7 +4672,7 @@
         <v>150.5243792360934</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>6.681270536692208</v>
+        <v>9.754208042819922</v>
       </c>
       <c r="M57" s="13" t="n">
         <v>0.2264756191470892</v>
@@ -4745,7 +4745,7 @@
         <v>114.7906219755248</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>8.009509006125981</v>
+        <v>11.19164156626507</v>
       </c>
       <c r="M58" s="13" t="n">
         <v>0.2195058768040626</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="K59" s="12" t="n"/>
       <c r="L59" s="12" t="n">
-        <v>7.55887198371934</v>
+        <v>12.35511464291137</v>
       </c>
       <c r="M59" s="13" t="n">
         <v>0.2180765993757863</v>
@@ -4885,7 +4885,7 @@
         <v>30.76413288208192</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>4.79139504563233</v>
+        <v>12.6094570928196</v>
       </c>
       <c r="M60" s="13" t="n">
         <v>0.2098023571281319</v>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="K61" s="12" t="n"/>
       <c r="L61" s="12" t="n">
-        <v>9.974945192608843</v>
+        <v>13.91727493917276</v>
       </c>
       <c r="M61" s="13" t="n">
         <v>0.2091942829854483</v>
@@ -5025,7 +5025,7 @@
         <v>39.90899502775312</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>7.642487046632107</v>
+        <v>11.2449799196787</v>
       </c>
       <c r="M62" s="13" t="n">
         <v>0.2079814708518931</v>
@@ -5098,7 +5098,7 @@
         <v>149.7303672867718</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>6.312542837559976</v>
+        <v>10.2965227903008</v>
       </c>
       <c r="M63" s="13" t="n">
         <v>0.2069424864759201</v>
@@ -5171,7 +5171,7 @@
         <v>86.4824992119545</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>3.212711667826484</v>
+        <v>7.670901391409535</v>
       </c>
       <c r="M64" s="13" t="n">
         <v>0.2023537292343684</v>
@@ -5244,7 +5244,7 @@
         <v>213.5610241247651</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>8.493298640090341</v>
+        <v>13.15412186379927</v>
       </c>
       <c r="M65" s="13" t="n">
         <v>0.2016914460536324</v>
@@ -5313,7 +5313,7 @@
         <v>95.90348696711568</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>2.936872909698973</v>
+        <v>7.557060172545604</v>
       </c>
       <c r="M66" s="13" t="n">
         <v>0.1931289589506998</v>
@@ -5386,7 +5386,7 @@
         <v>86.85614232849146</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3.037302228894778</v>
+        <v>7.481026382363565</v>
       </c>
       <c r="M67" s="13" t="n">
         <v>0.1930397734588009</v>
@@ -5459,7 +5459,7 @@
         <v>39.8311002358055</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>7.636363636363641</v>
+        <v>11.06941838649154</v>
       </c>
       <c r="M68" s="13" t="n">
         <v>0.1914465845545051</v>
@@ -5532,7 +5532,7 @@
         <v>87.11382196920727</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3.093259464450582</v>
+        <v>7.523775129408938</v>
       </c>
       <c r="M69" s="13" t="n">
         <v>0.1852616466175038</v>
@@ -5605,7 +5605,7 @@
         <v>860.7499017406718</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>2.965918769762088</v>
+        <v>6.851919118537353</v>
       </c>
       <c r="M70" s="13" t="n">
         <v>0.1828022459972292</v>
@@ -5678,7 +5678,7 @@
         <v>86.66560787154332</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>3.190013869625519</v>
+        <v>7.826086956521738</v>
       </c>
       <c r="M71" s="13" t="n">
         <v>0.1657634698136505</v>
@@ -5751,7 +5751,7 @@
         <v>688.0979293065751</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>10.8370839839564</v>
+        <v>14.81833896316031</v>
       </c>
       <c r="M72" s="13" t="n">
         <v>0.1653594897015658</v>
@@ -5824,7 +5824,7 @@
         <v>70.22875272047494</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>10.67247072951065</v>
+        <v>14.20384138785627</v>
       </c>
       <c r="M73" s="13" t="n">
         <v>0.164500870770665</v>
@@ -5897,7 +5897,7 @@
         <v>68.26956424915849</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>10.48176081268277</v>
+        <v>14.22660725652449</v>
       </c>
       <c r="M74" s="13" t="n">
         <v>0.1632330885320655</v>
@@ -5970,7 +5970,7 @@
         <v>14.05454109693392</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>4.867573371510381</v>
+        <v>12.08875286916602</v>
       </c>
       <c r="M75" s="13" t="n">
         <v>0.1621927538534075</v>
@@ -6043,7 +6043,7 @@
         <v>714.494528651919</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>10.64114832535885</v>
+        <v>14.44386916001705</v>
       </c>
       <c r="M76" s="13" t="n">
         <v>0.1498924838633819</v>
@@ -6116,7 +6116,7 @@
         <v>70.49199410693396</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>10.36385326573219</v>
+        <v>14.00184842883549</v>
       </c>
       <c r="M77" s="13" t="n">
         <v>0.1426229043616453</v>
@@ -6189,7 +6189,7 @@
         <v>721.1573306115982</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>10.39869433434366</v>
+        <v>14.41170696346861</v>
       </c>
       <c r="M78" s="13" t="n">
         <v>0.1392484651438273</v>
@@ -6262,7 +6262,7 @@
         <v>49.8766715971249</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>3.2258064516129</v>
+        <v>7.744107744107742</v>
       </c>
       <c r="M79" s="13" t="n">
         <v>0.1225927159311939</v>
@@ -6335,7 +6335,7 @@
         <v>23.32072465206712</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>10.43165467625899</v>
+        <v>14.60569295380307</v>
       </c>
       <c r="M80" s="13" t="n">
         <v>0.1045381050092817</v>
@@ -6408,7 +6408,7 @@
         <v>66.70512660323467</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>10.16708701134932</v>
+        <v>14.05026109660574</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>0.1003681208781735</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="K82" s="12" t="n"/>
       <c r="L82" s="12" t="n">
-        <v>7.523204689789953</v>
+        <v>13.39515713549717</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>0.07706933742746309</v>
@@ -6548,7 +6548,7 @@
         <v>67.10167896997754</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>9.940513462742651</v>
+        <v>13.82495948136142</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>0.07402052484345531</v>
@@ -6621,7 +6621,7 @@
         <v>47.03676922095357</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>7.970854493265622</v>
+        <v>13.80032580870374</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>0.05688149681182586</v>
@@ -6694,7 +6694,7 @@
         <v>21.58387431155958</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>7.62955854126679</v>
+        <v>13.2256436143362</v>
       </c>
       <c r="M85" s="13" t="n">
         <v>0.04315510445165875</v>
@@ -6767,7 +6767,7 @@
         <v>57.90205570746642</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>8.241857117149532</v>
+        <v>13.2128740824393</v>
       </c>
       <c r="M86" s="13" t="n">
         <v>0.02304902388448808</v>
@@ -6840,7 +6840,7 @@
         <v>22.97010995111894</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>-0.6872852233676952</v>
+        <v>1.760563380281699</v>
       </c>
       <c r="M87" s="13" t="n">
         <v>0.01420349970251947</v>
@@ -6913,7 +6913,7 @@
         <v>21.48359089586657</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>8.232445520581134</v>
+        <v>13.16455696202532</v>
       </c>
       <c r="M88" s="13" t="n">
         <v>0.003116098713545318</v>
@@ -6986,7 +6986,7 @@
         <v>192.1245759147101</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>9.151603973294264</v>
+        <v>13.66796676276072</v>
       </c>
       <c r="M89" s="13" t="n">
         <v>-0.001786910548328052</v>
@@ -7059,7 +7059,7 @@
         <v>49.00598236457562</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>7.384680490901396</v>
+        <v>13.30654163875866</v>
       </c>
       <c r="M90" s="13" t="n">
         <v>-0.007593241969580417</v>
@@ -7132,7 +7132,7 @@
         <v>24.43867802596036</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>8.404436860068266</v>
+        <v>14.45945945945946</v>
       </c>
       <c r="M91" s="13" t="n">
         <v>-0.009138331985724779</v>
@@ -7205,7 +7205,7 @@
         <v>10.62708422047197</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>8.3415112855741</v>
+        <v>13.23076923076922</v>
       </c>
       <c r="M92" s="13" t="n">
         <v>-0.01826534030009372</v>
@@ -7278,7 +7278,7 @@
         <v>21.66619963132241</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>8.11329812770043</v>
+        <v>13.39375629405841</v>
       </c>
       <c r="M93" s="13" t="n">
         <v>-0.02418593545401979</v>
@@ -7351,7 +7351,7 @@
         <v>41.84041501059995</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>11.51115618661258</v>
+        <v>17.12383488681757</v>
       </c>
       <c r="M94" s="13" t="n">
         <v>-0.02964210677432155</v>
@@ -7424,7 +7424,7 @@
         <v>219.4369013217262</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>7.76115162420683</v>
+        <v>12.94357040051615</v>
       </c>
       <c r="M95" s="13" t="n">
         <v>-0.03045567769893297</v>
@@ -7497,7 +7497,7 @@
         <v>62.10823553193526</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>8.085891628921328</v>
+        <v>13.29347634956921</v>
       </c>
       <c r="M96" s="13" t="n">
         <v>-0.0308796718727018</v>
@@ -7570,7 +7570,7 @@
         <v>63.26623812687077</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>1.279216677195194</v>
+        <v>1.648438738310332</v>
       </c>
       <c r="M97" s="13" t="n">
         <v>-0.03947134304044445</v>
@@ -7643,7 +7643,7 @@
         <v>16.75926858271935</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>5.792682926829285</v>
+        <v>13.17677756033921</v>
       </c>
       <c r="M98" s="13" t="n">
         <v>-0.05129966804747359</v>
@@ -7716,7 +7716,7 @@
         <v>21.95646244916327</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>7.524846190250822</v>
+        <v>12.25296442687747</v>
       </c>
       <c r="M99" s="13" t="n">
         <v>-0.05132169671618447</v>
@@ -7789,7 +7789,7 @@
         <v>32.99618448866452</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>8.667941363926079</v>
+        <v>12.134166392634</v>
       </c>
       <c r="M100" s="13" t="n">
         <v>-0.06539170984966339</v>
@@ -7862,7 +7862,7 @@
         <v>9.50858360592842</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>10.80178173719375</v>
+        <v>16.23831775700932</v>
       </c>
       <c r="M101" s="13" t="n">
         <v>-0.07928213233958914</v>
@@ -7935,7 +7935,7 @@
         <v>60.97092407469292</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>7.656652360515026</v>
+        <v>13.33815290077716</v>
       </c>
       <c r="M102" s="13" t="n">
         <v>-0.08945712521079274</v>
@@ -8008,7 +8008,7 @@
         <v>43.55294818508427</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>2.354570637119124</v>
+        <v>6.101938262742301</v>
       </c>
       <c r="M103" s="13" t="n">
         <v>-0.1026829947781038</v>
@@ -8081,7 +8081,7 @@
         <v>947.1637396757613</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>4.66104002178056</v>
+        <v>8.036557399163623</v>
       </c>
       <c r="M104" s="13" t="n">
         <v>-0.110552776153695</v>
@@ -8154,7 +8154,7 @@
         <v>12.93163921575373</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>7.748184019370452</v>
+        <v>12.27922624053825</v>
       </c>
       <c r="M105" s="13" t="n">
         <v>-0.1124227024520604</v>
@@ -8227,7 +8227,7 @@
         <v>40.30169914090978</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>9.765013054830284</v>
+        <v>15.27282698108035</v>
       </c>
       <c r="M106" s="13" t="n">
         <v>-0.1126391059862108</v>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="K107" s="12" t="n"/>
       <c r="L107" s="12" t="n">
-        <v>4.425514232287564</v>
+        <v>13.50496838301716</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>-0.1145340059702797</v>
@@ -8367,7 +8367,7 @@
         <v>94.25412218014009</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>4.352580927384087</v>
+        <v>8.038949275362327</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>-0.140616957786549</v>
@@ -8440,7 +8440,7 @@
         <v>158.834046705842</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>9.938259310894249</v>
+        <v>15.27217040233886</v>
       </c>
       <c r="M109" s="13" t="n">
         <v>-0.1460033796315825</v>
@@ -8513,7 +8513,7 @@
         <v>27.57917204975125</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>5.356469256884178</v>
+        <v>10.61386138613862</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>-0.1478938674825052</v>
@@ -8582,7 +8582,7 @@
         <v>144.7118370249401</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>5.51136763567257</v>
+        <v>12.27623398996331</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>-0.1569908680564051</v>
@@ -8651,7 +8651,7 @@
         <v>30.93116944103448</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>8.457374830852515</v>
+        <v>14.13314346742613</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>-0.1608219913901529</v>
@@ -8724,7 +8724,7 @@
         <v>15.83958952323838</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>9.786950732356846</v>
+        <v>15.39538138558432</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>-0.165445666838018</v>
@@ -8797,7 +8797,7 @@
         <v>42.87877871336121</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>7.41109176821686</v>
+        <v>12.18181818181818</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>-0.1814239107719172</v>
@@ -8866,7 +8866,7 @@
         <v>136.2083029765384</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>0.2261123267687903</v>
+        <v>-0.1961069145845484</v>
       </c>
       <c r="M115" s="13" t="n">
         <v>-0.1842021128898192</v>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="K116" s="12" t="n"/>
       <c r="L116" s="12" t="n">
-        <v>5.167343509312428</v>
+        <v>11.49049881235154</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>-0.1847903948715716</v>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="K117" s="12" t="n"/>
       <c r="L117" s="12" t="n">
-        <v>5.096262740656865</v>
+        <v>10.65182829888711</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>-0.1941517079948585</v>
@@ -9073,7 +9073,7 @@
         <v>510.0821204099516</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>11.1108803986711</v>
+        <v>18.70230700976043</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>-0.197887381557229</v>
@@ -9146,7 +9146,7 @@
         <v>14.84503785166933</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>0.2014775016789816</v>
+        <v>2.261823166552435</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>-0.2069899615516914</v>
@@ -9219,7 +9219,7 @@
         <v>148.1123770794378</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>-0.3420523138832898</v>
+        <v>2.880288028802869</v>
       </c>
       <c r="M120" s="13" t="n">
         <v>-0.2405672362663635</v>
@@ -9292,7 +9292,7 @@
         <v>145.7514407219516</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>-0.5310819091713714</v>
+        <v>2.728359468391806</v>
       </c>
       <c r="M121" s="13" t="n">
         <v>-0.2622730971996406</v>
@@ -9365,7 +9365,7 @@
         <v>17.32720858970796</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>9.190505173463182</v>
+        <v>15.22157996146436</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>-0.2713697561958667</v>
@@ -9438,7 +9438,7 @@
         <v>146.8706350291362</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>0.1085481682496559</v>
+        <v>2.607607259578604</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>-0.2765760254823283</v>
@@ -9511,7 +9511,7 @@
         <v>29.61432143223572</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>0.7070707070707005</v>
+        <v>1.047297297297289</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>-0.2766858207886075</v>
@@ -9584,7 +9584,7 @@
         <v>111.4720007382313</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>0.906235980260206</v>
+        <v>0.1781578478531776</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>-0.298119783227812</v>
@@ -9657,7 +9657,7 @@
         <v>50.37594248448844</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>7.358137601330283</v>
+        <v>13.46660808435851</v>
       </c>
       <c r="M126" s="13" t="n">
         <v>-0.3020975693708838</v>
@@ -9730,7 +9730,7 @@
         <v>30.50660365017153</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>7.899275612280099</v>
+        <v>12.31597845601435</v>
       </c>
       <c r="M127" s="13" t="n">
         <v>-0.318265570129013</v>
@@ -9803,7 +9803,7 @@
         <v>63.90810846312648</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>0.7958801498127333</v>
+        <v>0.8745900359206749</v>
       </c>
       <c r="M128" s="13" t="n">
         <v>-0.3215076685673725</v>
@@ -9876,7 +9876,7 @@
         <v>10.19502768122361</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>7.289527720739208</v>
+        <v>13.3405639913232</v>
       </c>
       <c r="M129" s="13" t="n">
         <v>-0.3279675738295718</v>
@@ -9949,7 +9949,7 @@
         <v>64.11185796320807</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>0.4667081518357152</v>
+        <v>0.3418272218769447</v>
       </c>
       <c r="M130" s="13" t="n">
         <v>-0.3479332638969835</v>
@@ -10022,7 +10022,7 @@
         <v>30.66042805000088</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>7.534246575342474</v>
+        <v>13.11239193083573</v>
       </c>
       <c r="M131" s="13" t="n">
         <v>-0.3499227781373265</v>
@@ -10095,7 +10095,7 @@
         <v>235.5450606971471</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>8.478690882934735</v>
+        <v>12.84137673026562</v>
       </c>
       <c r="M132" s="13" t="n">
         <v>-0.3866464210878825</v>
@@ -10168,7 +10168,7 @@
         <v>60.98250788667318</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>6.941580756013743</v>
+        <v>12.48870413880354</v>
       </c>
       <c r="M133" s="13" t="n">
         <v>-0.3981351203600877</v>
@@ -10241,7 +10241,7 @@
         <v>30.41426825398972</v>
       </c>
       <c r="L134" s="12" t="n">
-        <v>6.706045865184151</v>
+        <v>12.53206302674974</v>
       </c>
       <c r="M134" s="13" t="n">
         <v>-0.4047262337908921</v>
@@ -10314,7 +10314,7 @@
         <v>32.37515248398061</v>
       </c>
       <c r="L135" s="12" t="n">
-        <v>5.509020618556715</v>
+        <v>8.803986710963452</v>
       </c>
       <c r="M135" s="13" t="n">
         <v>-0.405990503833731</v>
@@ -10387,7 +10387,7 @@
         <v>30.39790862118573</v>
       </c>
       <c r="L136" s="12" t="n">
-        <v>6.746987951807237</v>
+        <v>12.4773304316286</v>
       </c>
       <c r="M136" s="13" t="n">
         <v>-0.4209049198323475</v>
@@ -10460,7 +10460,7 @@
         <v>15.71969805522383</v>
       </c>
       <c r="L137" s="12" t="n">
-        <v>7.348029392117561</v>
+        <v>12.06415620641563</v>
       </c>
       <c r="M137" s="13" t="n">
         <v>-0.4236626735595965</v>
@@ -10533,7 +10533,7 @@
         <v>332.6420501814562</v>
       </c>
       <c r="L138" s="12" t="n">
-        <v>5.885307134561657</v>
+        <v>9.245765730755506</v>
       </c>
       <c r="M138" s="13" t="n">
         <v>-0.4304064404715533</v>
@@ -10606,7 +10606,7 @@
         <v>11.6482531917552</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>4.324324324324325</v>
+        <v>6.433823529411753</v>
       </c>
       <c r="M139" s="13" t="n">
         <v>-0.4410827407294621</v>
@@ -10679,7 +10679,7 @@
         <v>29.5513077925793</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>7.262969588550994</v>
+        <v>10.95484826054776</v>
       </c>
       <c r="M140" s="13" t="n">
         <v>-0.4628954396394596</v>
@@ -10752,7 +10752,7 @@
         <v>80.04913248279445</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>6.27855371361441</v>
+        <v>8.574476596879599</v>
       </c>
       <c r="M141" s="13" t="n">
         <v>-0.4777295301232364</v>
@@ -10825,7 +10825,7 @@
         <v>32.28056803012202</v>
       </c>
       <c r="L142" s="12" t="n">
-        <v>5.973522763965122</v>
+        <v>9.655863681924481</v>
       </c>
       <c r="M142" s="13" t="n">
         <v>-0.4815445417338208</v>
@@ -10898,7 +10898,7 @@
         <v>27.13910987939712</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>5.501743510267354</v>
+        <v>10.42173560421735</v>
       </c>
       <c r="M143" s="13" t="n">
         <v>-0.483489652551657</v>
@@ -11044,7 +11044,7 @@
         <v>32.1436012721465</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>11.78063642518621</v>
+        <v>17.21689740859069</v>
       </c>
       <c r="M145" s="13" t="n">
         <v>-0.4885981126231584</v>
@@ -11117,7 +11117,7 @@
         <v>15.9927085040453</v>
       </c>
       <c r="L146" s="12" t="n">
-        <v>5.890052356020936</v>
+        <v>10.44368600682592</v>
       </c>
       <c r="M146" s="13" t="n">
         <v>-0.4895572798683223</v>
@@ -11190,7 +11190,7 @@
         <v>25.98582684886404</v>
       </c>
       <c r="L147" s="12" t="n">
-        <v>1.270207852193983</v>
+        <v>1.309202926453601</v>
       </c>
       <c r="M147" s="13" t="n">
         <v>-0.4912555632760515</v>
@@ -11263,7 +11263,7 @@
         <v>57.24150925353364</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>5.318559556786706</v>
+        <v>10.03279953694771</v>
       </c>
       <c r="M148" s="13" t="n">
         <v>-0.4957841785547426</v>
@@ -11336,7 +11336,7 @@
         <v>270.9594970235516</v>
       </c>
       <c r="L149" s="12" t="n">
-        <v>5.361088498662636</v>
+        <v>10.37563451776651</v>
       </c>
       <c r="M149" s="13" t="n">
         <v>-0.5012552818118569</v>
@@ -11409,7 +11409,7 @@
         <v>29.44179179520683</v>
       </c>
       <c r="L150" s="12" t="n">
-        <v>6.379928315412187</v>
+        <v>10.62243756988446</v>
       </c>
       <c r="M150" s="13" t="n">
         <v>-0.5148374871846436</v>
@@ -11482,7 +11482,7 @@
         <v>29.49908429923411</v>
       </c>
       <c r="L151" s="12" t="n">
-        <v>6.812477590534227</v>
+        <v>11.03242638837123</v>
       </c>
       <c r="M151" s="13" t="n">
         <v>-0.5299013280766971</v>
@@ -11555,7 +11555,7 @@
         <v>29.46779290296077</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>5.913978494623673</v>
+        <v>9.080841638981173</v>
       </c>
       <c r="M152" s="13" t="n">
         <v>-0.5347861039341788</v>
@@ -11628,7 +11628,7 @@
         <v>322.2729937939408</v>
       </c>
       <c r="L153" s="12" t="n">
-        <v>5.712713619886078</v>
+        <v>9.34382323401406</v>
       </c>
       <c r="M153" s="13" t="n">
         <v>-0.5406747293230346</v>
@@ -11701,7 +11701,7 @@
         <v>110.2496453579158</v>
       </c>
       <c r="L154" s="12" t="n">
-        <v>0.2807971014492594</v>
+        <v>1.336384439359262</v>
       </c>
       <c r="M154" s="13" t="n">
         <v>-0.60396877165862</v>
@@ -11774,7 +11774,7 @@
         <v>11.4114542282776</v>
       </c>
       <c r="L155" s="12" t="n">
-        <v>7.109879963065557</v>
+        <v>11.00478468899522</v>
       </c>
       <c r="M155" s="13" t="n">
         <v>-0.6215509032733989</v>
@@ -11847,7 +11847,7 @@
         <v>23.04547160879889</v>
       </c>
       <c r="L156" s="12" t="n">
-        <v>6.61798265632132</v>
+        <v>10.65845570819517</v>
       </c>
       <c r="M156" s="13" t="n">
         <v>-0.6309920048900377</v>
@@ -11920,7 +11920,7 @@
         <v>38.14708666823284</v>
       </c>
       <c r="L157" s="12" t="n">
-        <v>6.506754893851663</v>
+        <v>10.65597250071615</v>
       </c>
       <c r="M157" s="13" t="n">
         <v>-0.6564014421647248</v>
@@ -11993,7 +11993,7 @@
         <v>36.29005071603961</v>
       </c>
       <c r="L158" s="12" t="n">
-        <v>6.153846153846154</v>
+        <v>10.08428657435281</v>
       </c>
       <c r="M158" s="13" t="n">
         <v>-0.6664887025123778</v>
@@ -12066,7 +12066,7 @@
         <v>29.30430775537931</v>
       </c>
       <c r="L159" s="12" t="n">
-        <v>5.567606652205348</v>
+        <v>9.56848030018762</v>
       </c>
       <c r="M159" s="13" t="n">
         <v>-0.6914948120743744</v>
@@ -12135,7 +12135,7 @@
         <v>27.36121579997873</v>
       </c>
       <c r="L160" s="12" t="n">
-        <v>5.673485140872248</v>
+        <v>10.58158319870759</v>
       </c>
       <c r="M160" s="13" t="n">
         <v>-0.715559944000472</v>
@@ -12208,7 +12208,7 @@
         <v>20.94616021475341</v>
       </c>
       <c r="L161" s="12" t="n">
-        <v>8.04480651731161</v>
+        <v>10.29106029106028</v>
       </c>
       <c r="M161" s="13" t="n">
         <v>-0.7316397846293472</v>
@@ -12281,7 +12281,7 @@
         <v>11.13050532143652</v>
       </c>
       <c r="L162" s="12" t="n">
-        <v>5.849056603773595</v>
+        <v>9.784735812133061</v>
       </c>
       <c r="M162" s="13" t="n">
         <v>-0.7394259454055629</v>
@@ -12354,7 +12354,7 @@
         <v>20.32874778817504</v>
       </c>
       <c r="L163" s="12" t="n">
-        <v>7.571801566579639</v>
+        <v>11.41157382368849</v>
       </c>
       <c r="M163" s="13" t="n">
         <v>-0.7559877477605004</v>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="K164" s="12" t="n"/>
       <c r="L164" s="12" t="n">
-        <v>8.383802398764995</v>
+        <v>11.27773713728359</v>
       </c>
       <c r="M164" s="13" t="n">
         <v>-0.7888748183493445</v>
@@ -12494,7 +12494,7 @@
         <v>25.97967871274014</v>
       </c>
       <c r="L165" s="12" t="n">
-        <v>5.571370475803183</v>
+        <v>9.029819403611938</v>
       </c>
       <c r="M165" s="13" t="n">
         <v>-0.7995063224555911</v>
@@ -12567,7 +12567,7 @@
         <v>576.7771543839037</v>
       </c>
       <c r="L166" s="12" t="n">
-        <v>5.383824663166781</v>
+        <v>9.951163458776225</v>
       </c>
       <c r="M166" s="13" t="n">
         <v>-0.8362019814742263</v>
@@ -12640,7 +12640,7 @@
         <v>58.79317470771069</v>
       </c>
       <c r="L167" s="12" t="n">
-        <v>5.356176735798024</v>
+        <v>8.627742655262182</v>
       </c>
       <c r="M167" s="13" t="n">
         <v>-0.8383559690779583</v>
@@ -12713,7 +12713,7 @@
         <v>25.33077603206454</v>
       </c>
       <c r="L168" s="12" t="n">
-        <v>5.673758865248235</v>
+        <v>9.086993970714907</v>
       </c>
       <c r="M168" s="13" t="n">
         <v>-0.846088757308507</v>
@@ -12786,7 +12786,7 @@
         <v>58.27721320079635</v>
       </c>
       <c r="L169" s="12" t="n">
-        <v>5.327272727272736</v>
+        <v>9.715909090909092</v>
       </c>
       <c r="M169" s="13" t="n">
         <v>-0.8487144004722795</v>
@@ -12859,7 +12859,7 @@
         <v>57.176176882549</v>
       </c>
       <c r="L170" s="12" t="n">
-        <v>5.049010541890131</v>
+        <v>10.61343719571566</v>
       </c>
       <c r="M170" s="13" t="n">
         <v>-0.8513212112733979</v>
@@ -12932,7 +12932,7 @@
         <v>217.8016443112231</v>
       </c>
       <c r="L171" s="12" t="n">
-        <v>7.521176126959417</v>
+        <v>10.62860005008766</v>
       </c>
       <c r="M171" s="13" t="n">
         <v>-0.8550575453542701</v>
@@ -13005,7 +13005,7 @@
         <v>583.884419168701</v>
       </c>
       <c r="L172" s="12" t="n">
-        <v>5.212488215244027</v>
+        <v>9.736772436745934</v>
       </c>
       <c r="M172" s="13" t="n">
         <v>-0.8593605027474892</v>
@@ -13078,7 +13078,7 @@
         <v>58.0506986886069</v>
       </c>
       <c r="L173" s="12" t="n">
-        <v>5.310218978102199</v>
+        <v>9.777439604337079</v>
       </c>
       <c r="M173" s="13" t="n">
         <v>-0.8618179486585329</v>
@@ -13151,7 +13151,7 @@
         <v>586.4353413118401</v>
       </c>
       <c r="L174" s="12" t="n">
-        <v>5.342587070071758</v>
+        <v>9.626271935599174</v>
       </c>
       <c r="M174" s="13" t="n">
         <v>-0.8643712544160712</v>
@@ -13224,7 +13224,7 @@
         <v>57.97167126745606</v>
       </c>
       <c r="L175" s="12" t="n">
-        <v>5.034658883619114</v>
+        <v>9.613554159527894</v>
       </c>
       <c r="M175" s="13" t="n">
         <v>-0.8735514110607212</v>
@@ -13297,7 +13297,7 @@
         <v>581.9136135999951</v>
       </c>
       <c r="L176" s="12" t="n">
-        <v>5.271303714493802</v>
+        <v>9.419357280744922</v>
       </c>
       <c r="M176" s="13" t="n">
         <v>-0.8791164937867565</v>
@@ -13370,7 +13370,7 @@
         <v>11.02558556159753</v>
       </c>
       <c r="L177" s="12" t="n">
-        <v>8.390243902439011</v>
+        <v>13.59918200408998</v>
       </c>
       <c r="M177" s="13" t="n">
         <v>-0.8871476368033813</v>
@@ -13443,7 +13443,7 @@
         <v>58.14840093033335</v>
       </c>
       <c r="L178" s="12" t="n">
-        <v>5.322639445862198</v>
+        <v>9.889691898060104</v>
       </c>
       <c r="M178" s="13" t="n">
         <v>-0.8897467157977095</v>
@@ -13516,7 +13516,7 @@
         <v>27.66016761569319</v>
       </c>
       <c r="L179" s="12" t="n">
-        <v>6.266924564796894</v>
+        <v>10.5877616747182</v>
       </c>
       <c r="M179" s="13" t="n">
         <v>-0.8973296492064189</v>
@@ -13589,7 +13589,7 @@
         <v>42.89230608486336</v>
       </c>
       <c r="L180" s="12" t="n">
-        <v>7.634730538922163</v>
+        <v>12.66649255680334</v>
       </c>
       <c r="M180" s="13" t="n">
         <v>-0.906974506965682</v>
@@ -13662,7 +13662,7 @@
         <v>1392.438301624289</v>
       </c>
       <c r="L181" s="12" t="n">
-        <v>1.11461755720792</v>
+        <v>1.026541792344848</v>
       </c>
       <c r="M181" s="13" t="n">
         <v>-0.9126013945623586</v>
@@ -13735,7 +13735,7 @@
         <v>57.56410393230706</v>
       </c>
       <c r="L182" s="12" t="n">
-        <v>4.990825688073386</v>
+        <v>8.043806646525686</v>
       </c>
       <c r="M182" s="13" t="n">
         <v>-0.9150469450049463</v>
@@ -13808,7 +13808,7 @@
         <v>274.6532108324299</v>
       </c>
       <c r="L183" s="12" t="n">
-        <v>5.714505460698338</v>
+        <v>8.914421553090325</v>
       </c>
       <c r="M183" s="13" t="n">
         <v>-0.9174306152029817</v>
@@ -13881,7 +13881,7 @@
         <v>281.2702812261618</v>
       </c>
       <c r="L184" s="12" t="n">
-        <v>4.500167916713305</v>
+        <v>11.11772408046661</v>
       </c>
       <c r="M184" s="13" t="n">
         <v>-0.9297146691017901</v>
@@ -13954,7 +13954,7 @@
         <v>20.3846275750248</v>
       </c>
       <c r="L185" s="12" t="n">
-        <v>5.206185567010313</v>
+        <v>8.506113769271661</v>
       </c>
       <c r="M185" s="13" t="n">
         <v>-0.9347572368998378</v>
@@ -14027,7 +14027,7 @@
         <v>10.29791764768249</v>
       </c>
       <c r="L186" s="12" t="n">
-        <v>4.352226720647767</v>
+        <v>6.618407445708385</v>
       </c>
       <c r="M186" s="13" t="n">
         <v>-0.937803943098402</v>
@@ -14100,7 +14100,7 @@
         <v>270.3188622827005</v>
       </c>
       <c r="L187" s="12" t="n">
-        <v>5.325653871947611</v>
+        <v>7.887824786842845</v>
       </c>
       <c r="M187" s="13" t="n">
         <v>-0.9623276004656383</v>
@@ -14173,7 +14173,7 @@
         <v>78.85684666282208</v>
       </c>
       <c r="L188" s="12" t="n">
-        <v>13.64556230124312</v>
+        <v>18.40361445783132</v>
       </c>
       <c r="M188" s="13" t="n">
         <v>-0.9679982049276539</v>
@@ -14246,7 +14246,7 @@
         <v>10.51927259847361</v>
       </c>
       <c r="L189" s="12" t="n">
-        <v>5.728643216080398</v>
+        <v>9.12863070539418</v>
       </c>
       <c r="M189" s="13" t="n">
         <v>-0.9715375593141129</v>
@@ -14319,7 +14319,7 @@
         <v>266.5564266432809</v>
       </c>
       <c r="L190" s="12" t="n">
-        <v>5.461736207237511</v>
+        <v>9.036637226038602</v>
       </c>
       <c r="M190" s="13" t="n">
         <v>-0.9767272138801326</v>
@@ -14392,7 +14392,7 @@
         <v>28.0505585793335</v>
       </c>
       <c r="L191" s="12" t="n">
-        <v>5.840241145440839</v>
+        <v>9.427347097779503</v>
       </c>
       <c r="M191" s="13" t="n">
         <v>-0.9917786115000902</v>
@@ -14465,7 +14465,7 @@
         <v>8.825529954237734</v>
       </c>
       <c r="L192" s="12" t="n">
-        <v>13.82428940568476</v>
+        <v>18.57335127860027</v>
       </c>
       <c r="M192" s="13" t="n">
         <v>-0.998595648379085</v>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="K193" s="12" t="n"/>
       <c r="L193" s="12" t="n">
-        <v>5.167118337850041</v>
+        <v>9.768055817461807</v>
       </c>
       <c r="M193" s="13" t="n">
         <v>-1.005199486183527</v>
@@ -14605,7 +14605,7 @@
         <v>20.68748008155402</v>
       </c>
       <c r="L194" s="12" t="n">
-        <v>7.475678443420364</v>
+        <v>10.7067510548523</v>
       </c>
       <c r="M194" s="13" t="n">
         <v>-1.01012755326029</v>
@@ -14678,7 +14678,7 @@
         <v>1269.750695805121</v>
       </c>
       <c r="L195" s="12" t="n">
-        <v>1.265933021930166</v>
+        <v>1.144217235216916</v>
       </c>
       <c r="M195" s="13" t="n">
         <v>-1.01337408511761</v>
@@ -14751,7 +14751,7 @@
         <v>27.67013017708957</v>
       </c>
       <c r="L196" s="12" t="n">
-        <v>6.573859242072699</v>
+        <v>10.72719967858577</v>
       </c>
       <c r="M196" s="13" t="n">
         <v>-1.019143103998351</v>
@@ -14824,7 +14824,7 @@
         <v>1559.793698938395</v>
       </c>
       <c r="L197" s="12" t="n">
-        <v>0.7322707633221404</v>
+        <v>1.173301520682357</v>
       </c>
       <c r="M197" s="13" t="n">
         <v>-1.030729196436476</v>
@@ -14897,7 +14897,7 @@
         <v>26.86961196545344</v>
       </c>
       <c r="L198" s="12" t="n">
-        <v>2.857142857142869</v>
+        <v>6.773547094188381</v>
       </c>
       <c r="M198" s="13" t="n">
         <v>-1.044143206106205</v>
@@ -14970,7 +14970,7 @@
         <v>27.44264780902792</v>
       </c>
       <c r="L199" s="12" t="n">
-        <v>5.790905557714732</v>
+        <v>9.935379644588039</v>
       </c>
       <c r="M199" s="13" t="n">
         <v>-1.054927724546488</v>
@@ -15043,7 +15043,7 @@
         <v>57.11019449060819</v>
       </c>
       <c r="L200" s="12" t="n">
-        <v>6.271905552481094</v>
+        <v>9.58721704394141</v>
       </c>
       <c r="M200" s="13" t="n">
         <v>-1.055669724233847</v>
@@ -15116,7 +15116,7 @@
         <v>277.5376219867976</v>
       </c>
       <c r="L201" s="12" t="n">
-        <v>6.874999999999987</v>
+        <v>10.39778651054615</v>
       </c>
       <c r="M201" s="13" t="n">
         <v>-1.058382039458538</v>
@@ -15189,7 +15189,7 @@
         <v>255.438085386904</v>
       </c>
       <c r="L202" s="12" t="n">
-        <v>4.694138514210278</v>
+        <v>8.262241938235793</v>
       </c>
       <c r="M202" s="13" t="n">
         <v>-1.072267400355263</v>
@@ -15262,7 +15262,7 @@
         <v>148.092693631228</v>
       </c>
       <c r="L203" s="12" t="n">
-        <v>5.357651752636072</v>
+        <v>7.377287249491715</v>
       </c>
       <c r="M203" s="13" t="n">
         <v>-1.07239851508014</v>
@@ -15335,7 +15335,7 @@
         <v>251.4021282810748</v>
       </c>
       <c r="L204" s="12" t="n">
-        <v>3.796361819922578</v>
+        <v>8.140341746899104</v>
       </c>
       <c r="M204" s="13" t="n">
         <v>-1.082950682092196</v>
@@ -15408,7 +15408,7 @@
         <v>20.82831730204153</v>
       </c>
       <c r="L205" s="12" t="n">
-        <v>5.332656170644978</v>
+        <v>8.814270724029383</v>
       </c>
       <c r="M205" s="13" t="n">
         <v>-1.083309817822045</v>
@@ -15481,7 +15481,7 @@
         <v>24.742468549167</v>
       </c>
       <c r="L206" s="12" t="n">
-        <v>4.362703165098369</v>
+        <v>8.540925266903908</v>
       </c>
       <c r="M206" s="13" t="n">
         <v>-1.10706038397033</v>
@@ -15550,7 +15550,7 @@
         <v>41.69712808976456</v>
       </c>
       <c r="L207" s="12" t="n">
-        <v>5.472510767671657</v>
+        <v>8.893539105414616</v>
       </c>
       <c r="M207" s="13" t="n">
         <v>-1.11244050239199</v>
@@ -15623,7 +15623,7 @@
         <v>10.07082786694145</v>
       </c>
       <c r="L208" s="12" t="n">
-        <v>4.602510460251041</v>
+        <v>8.225108225108224</v>
       </c>
       <c r="M208" s="13" t="n">
         <v>-1.140080308401666</v>
@@ -15696,7 +15696,7 @@
         <v>273.618699565151</v>
       </c>
       <c r="L209" s="12" t="n">
-        <v>4.767589632995728</v>
+        <v>8.498843423466539</v>
       </c>
       <c r="M209" s="13" t="n">
         <v>-1.149688864595458</v>
@@ -15769,7 +15769,7 @@
         <v>118.0380085051994</v>
       </c>
       <c r="L210" s="12" t="n">
-        <v>5.944055944055937</v>
+        <v>10.45989904655076</v>
       </c>
       <c r="M210" s="13" t="n">
         <v>-1.15007132419866</v>
@@ -15842,7 +15842,7 @@
         <v>80.38394400961461</v>
       </c>
       <c r="L211" s="12" t="n">
-        <v>4.669673653489004</v>
+        <v>8.260153677277726</v>
       </c>
       <c r="M211" s="13" t="n">
         <v>-1.155954528258872</v>
@@ -15911,7 +15911,7 @@
         <v>2799.517869146028</v>
       </c>
       <c r="L212" s="12" t="n">
-        <v>4.091357142857155</v>
+        <v>7.527382524271853</v>
       </c>
       <c r="M212" s="13" t="n">
         <v>-1.156411614753749</v>
@@ -15984,7 +15984,7 @@
         <v>1308.016519346444</v>
       </c>
       <c r="L213" s="12" t="n">
-        <v>1.124139501178645</v>
+        <v>0.6154263696273699</v>
       </c>
       <c r="M213" s="13" t="n">
         <v>-1.159707595061679</v>
@@ -16057,7 +16057,7 @@
         <v>28.69100868551509</v>
       </c>
       <c r="L214" s="12" t="n">
-        <v>0.7684247293049395</v>
+        <v>0.9800490024501229</v>
       </c>
       <c r="M214" s="13" t="n">
         <v>-1.163690192850439</v>
@@ -16130,7 +16130,7 @@
         <v>265.3777934036606</v>
       </c>
       <c r="L215" s="12" t="n">
-        <v>4.577394894596853</v>
+        <v>8.269625976161121</v>
       </c>
       <c r="M215" s="13" t="n">
         <v>-1.166031600148966</v>
@@ -16203,7 +16203,7 @@
         <v>275.09498504042</v>
       </c>
       <c r="L216" s="12" t="n">
-        <v>4.515165441176472</v>
+        <v>8.143128863528304</v>
       </c>
       <c r="M216" s="13" t="n">
         <v>-1.171851530755821</v>
@@ -16276,7 +16276,7 @@
         <v>265.7875500011189</v>
       </c>
       <c r="L217" s="12" t="n">
-        <v>4.523431294678315</v>
+        <v>7.358759942892101</v>
       </c>
       <c r="M217" s="13" t="n">
         <v>-1.185095222353581</v>
@@ -16349,7 +16349,7 @@
         <v>893.9218191018064</v>
       </c>
       <c r="L218" s="12" t="n">
-        <v>3.597223856016929</v>
+        <v>8.359376922509032</v>
       </c>
       <c r="M218" s="13" t="n">
         <v>-1.188959299968663</v>
@@ -16422,7 +16422,7 @@
         <v>270.2928003970207</v>
       </c>
       <c r="L219" s="12" t="n">
-        <v>4.838835862932256</v>
+        <v>8.094700330725168</v>
       </c>
       <c r="M219" s="13" t="n">
         <v>-1.1934136180092</v>
@@ -16495,7 +16495,7 @@
         <v>270.835892273964</v>
       </c>
       <c r="L220" s="12" t="n">
-        <v>4.766920226253157</v>
+        <v>8.080808080808065</v>
       </c>
       <c r="M220" s="13" t="n">
         <v>-1.19548091785882</v>
@@ -16568,7 +16568,7 @@
         <v>133.1491558935665</v>
       </c>
       <c r="L221" s="12" t="n">
-        <v>5.353048153712359</v>
+        <v>6.040588937524882</v>
       </c>
       <c r="M221" s="13" t="n">
         <v>-1.197594519023383</v>
@@ -16641,7 +16641,7 @@
         <v>276.7199914207307</v>
       </c>
       <c r="L222" s="12" t="n">
-        <v>4.473804447151997</v>
+        <v>8.065850104367689</v>
       </c>
       <c r="M222" s="13" t="n">
         <v>-1.205535787580837</v>
@@ -16714,7 +16714,7 @@
         <v>126.9098718675785</v>
       </c>
       <c r="L223" s="12" t="n">
-        <v>6.192468619246871</v>
+        <v>10.35742238455519</v>
       </c>
       <c r="M223" s="13" t="n">
         <v>-1.21367403961001</v>
@@ -16787,7 +16787,7 @@
         <v>117.4451545265805</v>
       </c>
       <c r="L224" s="12" t="n">
-        <v>5.762098597919496</v>
+        <v>9.742819598272945</v>
       </c>
       <c r="M224" s="13" t="n">
         <v>-1.220463857211344</v>
@@ -16860,7 +16860,7 @@
         <v>278.0755861169304</v>
       </c>
       <c r="L225" s="12" t="n">
-        <v>4.472468378398853</v>
+        <v>8.120713305898498</v>
       </c>
       <c r="M225" s="13" t="n">
         <v>-1.220620674832896</v>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="K226" s="12" t="n"/>
       <c r="L226" s="12" t="n">
-        <v>3.897324656543755</v>
+        <v>7.760764952190491</v>
       </c>
       <c r="M226" s="13" t="n">
         <v>-1.222941888954679</v>
@@ -17000,7 +17000,7 @@
         <v>204.0175017498489</v>
       </c>
       <c r="L227" s="12" t="n">
-        <v>4.405874499332429</v>
+        <v>7.804878048780495</v>
       </c>
       <c r="M227" s="13" t="n">
         <v>-1.223271945781832</v>
@@ -17073,7 +17073,7 @@
         <v>28.60435304304229</v>
       </c>
       <c r="L228" s="12" t="n">
-        <v>4.607445632141549</v>
+        <v>8.155487804878048</v>
       </c>
       <c r="M228" s="13" t="n">
         <v>-1.225324359934685</v>
@@ -17146,7 +17146,7 @@
         <v>76.96100038615005</v>
       </c>
       <c r="L229" s="12" t="n">
-        <v>6.874282433983914</v>
+        <v>13.36580910336429</v>
       </c>
       <c r="M229" s="13" t="n">
         <v>-1.229672976427438</v>
@@ -17219,7 +17219,7 @@
         <v>14.76748349818401</v>
       </c>
       <c r="L230" s="12" t="n">
-        <v>5.195729537366534</v>
+        <v>6.560922855082918</v>
       </c>
       <c r="M230" s="13" t="n">
         <v>-1.231436199284082</v>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="K231" s="12" t="n"/>
       <c r="L231" s="12" t="n">
-        <v>4.336486433882203</v>
+        <v>7.850474810880392</v>
       </c>
       <c r="M231" s="13" t="n">
         <v>-1.233633443339155</v>
@@ -17359,7 +17359,7 @@
         <v>14.42500440626251</v>
       </c>
       <c r="L232" s="12" t="n">
-        <v>5.405405405405417</v>
+        <v>7.928197456993269</v>
       </c>
       <c r="M232" s="13" t="n">
         <v>-1.23758803301657</v>
@@ -17432,7 +17432,7 @@
         <v>262.8853800806994</v>
       </c>
       <c r="L233" s="12" t="n">
-        <v>4.373423044575286</v>
+        <v>8.024870466321254</v>
       </c>
       <c r="M233" s="13" t="n">
         <v>-1.24613327399744</v>
@@ -17505,7 +17505,7 @@
         <v>81.6134332270376</v>
       </c>
       <c r="L234" s="12" t="n">
-        <v>4.532467532467521</v>
+        <v>7.924376508447306</v>
       </c>
       <c r="M234" s="13" t="n">
         <v>-1.247744380054149</v>
@@ -17578,7 +17578,7 @@
         <v>257.1486369709731</v>
       </c>
       <c r="L235" s="12" t="n">
-        <v>4.507793273174721</v>
+        <v>7.993896494722996</v>
       </c>
       <c r="M235" s="13" t="n">
         <v>-1.248124012487983</v>
@@ -17651,7 +17651,7 @@
         <v>37.08131682275915</v>
       </c>
       <c r="L236" s="12" t="n">
-        <v>3.719477569562746</v>
+        <v>6.284550480069839</v>
       </c>
       <c r="M236" s="13" t="n">
         <v>-1.249618903460468</v>
@@ -17724,7 +17724,7 @@
         <v>9.872313941203942</v>
       </c>
       <c r="L237" s="12" t="n">
-        <v>4.482390608324449</v>
+        <v>7.938257993384767</v>
       </c>
       <c r="M237" s="13" t="n">
         <v>-1.251062006993006</v>
@@ -17797,7 +17797,7 @@
         <v>9.810107769867136</v>
       </c>
       <c r="L238" s="12" t="n">
-        <v>4.418103448275867</v>
+        <v>7.906458797327387</v>
       </c>
       <c r="M238" s="13" t="n">
         <v>-1.277240353715982</v>
@@ -17870,7 +17870,7 @@
         <v>117.5534754505662</v>
       </c>
       <c r="L239" s="12" t="n">
-        <v>5.841521680338935</v>
+        <v>10.24413145539906</v>
       </c>
       <c r="M239" s="13" t="n">
         <v>-1.28467007390233</v>
@@ -17943,7 +17943,7 @@
         <v>79.74042777230454</v>
       </c>
       <c r="L240" s="12" t="n">
-        <v>4.130808950086062</v>
+        <v>7.724969182303787</v>
       </c>
       <c r="M240" s="13" t="n">
         <v>-1.314660259439979</v>
@@ -18016,7 +18016,7 @@
         <v>258.7054075950529</v>
       </c>
       <c r="L241" s="12" t="n">
-        <v>-0.08504058755314237</v>
+        <v>-0.2007722007721924</v>
       </c>
       <c r="M241" s="13" t="n">
         <v>-1.321327343558304</v>
@@ -18089,7 +18089,7 @@
         <v>21.90237489926002</v>
       </c>
       <c r="L242" s="12" t="n">
-        <v>4.017216642754673</v>
+        <v>7.833415964303403</v>
       </c>
       <c r="M242" s="13" t="n">
         <v>-1.332724298187971</v>
@@ -18162,7 +18162,7 @@
         <v>29.7157872455073</v>
       </c>
       <c r="L243" s="12" t="n">
-        <v>0.3365870077414845</v>
+        <v>0.2690884628321566</v>
       </c>
       <c r="M243" s="13" t="n">
         <v>-1.356563494886715</v>
@@ -18235,7 +18235,7 @@
         <v>31.9023752152123</v>
       </c>
       <c r="L244" s="12" t="n">
-        <v>4.798657718120802</v>
+        <v>8.626086956521739</v>
       </c>
       <c r="M244" s="13" t="n">
         <v>-1.357401403070792</v>
@@ -18304,7 +18304,7 @@
         <v>89.80497203390814</v>
       </c>
       <c r="L245" s="12" t="n">
-        <v>4.389268063073648</v>
+        <v>7.736215691037152</v>
       </c>
       <c r="M245" s="13" t="n">
         <v>-1.363010131487948</v>
@@ -18377,7 +18377,7 @@
         <v>29.15558000146961</v>
       </c>
       <c r="L246" s="12" t="n">
-        <v>0.6526966678117585</v>
+        <v>0.5145797598627766</v>
       </c>
       <c r="M246" s="13" t="n">
         <v>-1.370623380253201</v>
@@ -18450,7 +18450,7 @@
         <v>910.2149903890993</v>
       </c>
       <c r="L247" s="12" t="n">
-        <v>4.27104150206814</v>
+        <v>7.610585512668333</v>
       </c>
       <c r="M247" s="13" t="n">
         <v>-1.388989918276284</v>
@@ -18523,7 +18523,7 @@
         <v>82.10955116807759</v>
       </c>
       <c r="L248" s="12" t="n">
-        <v>4.072689779610772</v>
+        <v>7.508986819331653</v>
       </c>
       <c r="M248" s="13" t="n">
         <v>-1.395922282323672</v>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="K249" s="12" t="n"/>
       <c r="L249" s="12" t="n">
-        <v>4.220398593200492</v>
+        <v>8.019441069258804</v>
       </c>
       <c r="M249" s="13" t="n">
         <v>-1.397056698776677</v>
@@ -18663,7 +18663,7 @@
         <v>9.258224671128593</v>
       </c>
       <c r="L250" s="12" t="n">
-        <v>9.004739336492884</v>
+        <v>14.00247831474597</v>
       </c>
       <c r="M250" s="13" t="n">
         <v>-1.403190452023621</v>
@@ -18736,7 +18736,7 @@
         <v>258.5495488517549</v>
       </c>
       <c r="L251" s="12" t="n">
-        <v>0.4311349335819115</v>
+        <v>0.2597906165180408</v>
       </c>
       <c r="M251" s="13" t="n">
         <v>-1.412433477738333</v>
@@ -18809,7 +18809,7 @@
         <v>81.62309986062139</v>
       </c>
       <c r="L252" s="12" t="n">
-        <v>4.160186625194418</v>
+        <v>7.73458445040216</v>
       </c>
       <c r="M252" s="13" t="n">
         <v>-1.414675742822821</v>
@@ -18882,7 +18882,7 @@
         <v>9.954022463055175</v>
       </c>
       <c r="L253" s="12" t="n">
-        <v>7.335490830636449</v>
+        <v>10.67853170189097</v>
       </c>
       <c r="M253" s="13" t="n">
         <v>-1.429148294201305</v>
@@ -18955,7 +18955,7 @@
         <v>12.47304596422314</v>
       </c>
       <c r="L254" s="12" t="n">
-        <v>8.691834942932397</v>
+        <v>13.99631675874771</v>
       </c>
       <c r="M254" s="13" t="n">
         <v>-1.429379470401694</v>
@@ -19028,7 +19028,7 @@
         <v>54.05556812040566</v>
       </c>
       <c r="L255" s="12" t="n">
-        <v>5.387205387205385</v>
+        <v>8.702757916241065</v>
       </c>
       <c r="M255" s="13" t="n">
         <v>-1.753086711030533</v>
@@ -19101,7 +19101,7 @@
         <v>10.26402862399123</v>
       </c>
       <c r="L256" s="12" t="n">
-        <v>4.153686396677037</v>
+        <v>8.081896551724132</v>
       </c>
       <c r="M256" s="13" t="n">
         <v>-1.773141142951928</v>
@@ -19174,7 +19174,7 @@
         <v>93.0161689632241</v>
       </c>
       <c r="L257" s="12" t="n">
-        <v>4.742077261161248</v>
+        <v>8.208866053291919</v>
       </c>
       <c r="M257" s="13" t="n">
         <v>-1.823072470849977</v>
@@ -19247,7 +19247,7 @@
         <v>481.1344525984621</v>
       </c>
       <c r="L258" s="12" t="n">
-        <v>5.055173481347164</v>
+        <v>7.999909066108946</v>
       </c>
       <c r="M258" s="13" t="n">
         <v>-2.009281665069499</v>
@@ -19320,7 +19320,7 @@
         <v>119.3208453783596</v>
       </c>
       <c r="L259" s="12" t="n">
-        <v>4.084003574620199</v>
+        <v>6.912061685331383</v>
       </c>
       <c r="M259" s="13" t="n">
         <v>-2.029264682835551</v>
@@ -19393,7 +19393,7 @@
         <v>36.37843001498084</v>
       </c>
       <c r="L260" s="12" t="n">
-        <v>7.190942472460216</v>
+        <v>8.890270438296554</v>
       </c>
       <c r="M260" s="13" t="n">
         <v>-2.079804799812567</v>
@@ -19466,7 +19466,7 @@
         <v>86.50281449364495</v>
       </c>
       <c r="L261" s="12" t="n">
-        <v>6.988564167725531</v>
+        <v>9.835637881554927</v>
       </c>
       <c r="M261" s="13" t="n">
         <v>-2.084858870899475</v>
@@ -19539,7 +19539,7 @@
         <v>34.80348739639938</v>
       </c>
       <c r="L262" s="12" t="n">
-        <v>7.362355953905242</v>
+        <v>9.250814332247547</v>
       </c>
       <c r="M262" s="13" t="n">
         <v>-2.116246279845968</v>
@@ -19612,7 +19612,7 @@
         <v>36.42457184000968</v>
       </c>
       <c r="L263" s="12" t="n">
-        <v>7.374541003671986</v>
+        <v>9.246575342465778</v>
       </c>
       <c r="M263" s="13" t="n">
         <v>-2.134963961651281</v>
@@ -19685,7 +19685,7 @@
         <v>361.8304741581376</v>
       </c>
       <c r="L264" s="12" t="n">
-        <v>7.338377314387645</v>
+        <v>9.325564639914784</v>
       </c>
       <c r="M264" s="13" t="n">
         <v>-2.146838839228963</v>
@@ -19758,7 +19758,7 @@
         <v>34.73181865670217</v>
       </c>
       <c r="L265" s="12" t="n">
-        <v>7.179487179487176</v>
+        <v>9.281045751633975</v>
       </c>
       <c r="M265" s="13" t="n">
         <v>-2.151716348701855</v>
@@ -19831,7 +19831,7 @@
         <v>35.7120802307211</v>
       </c>
       <c r="L266" s="12" t="n">
-        <v>7.361197754210846</v>
+        <v>9.269841269841272</v>
       </c>
       <c r="M266" s="13" t="n">
         <v>-2.16857204553494</v>
@@ -19904,7 +19904,7 @@
         <v>36.45859953341175</v>
       </c>
       <c r="L267" s="12" t="n">
-        <v>7.04697986577183</v>
+        <v>9.178593652769141</v>
       </c>
       <c r="M267" s="13" t="n">
         <v>-2.179964791175939</v>
@@ -19977,7 +19977,7 @@
         <v>345.0060068450187</v>
       </c>
       <c r="L268" s="12" t="n">
-        <v>7.625913234628579</v>
+        <v>9.282783522074523</v>
       </c>
       <c r="M268" s="13" t="n">
         <v>-2.183880260411754</v>
@@ -20050,7 +20050,7 @@
         <v>35.05365168857782</v>
       </c>
       <c r="L269" s="12" t="n">
-        <v>7.242693773824649</v>
+        <v>9.32642487046631</v>
       </c>
       <c r="M269" s="13" t="n">
         <v>-2.189471493890019</v>
@@ -20123,7 +20123,7 @@
         <v>364.099161433808</v>
       </c>
       <c r="L270" s="12" t="n">
-        <v>7.043890503135053</v>
+        <v>9.062013088189481</v>
       </c>
       <c r="M270" s="13" t="n">
         <v>-2.200711799854188</v>
@@ -20196,7 +20196,7 @@
         <v>1048.741620976973</v>
       </c>
       <c r="L271" s="12" t="n">
-        <v>0.3203761101790548</v>
+        <v>0.3631751286626628</v>
       </c>
       <c r="M271" s="13" t="n">
         <v>-10.37242228371417</v>
@@ -20269,7 +20269,7 @@
         <v>1027.208597523371</v>
       </c>
       <c r="L272" s="12" t="n">
-        <v>0.3059495570508775</v>
+        <v>0.3438389864982572</v>
       </c>
       <c r="M272" s="13" t="n">
         <v>-12.39135751149893</v>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="K273" s="12" t="n"/>
       <c r="L273" s="12" t="n">
-        <v>5.408099688473533</v>
+        <v>9.671982367431632</v>
       </c>
       <c r="M273" s="13" t="n"/>
       <c r="N273" s="13" t="n"/>
@@ -20401,7 +20401,7 @@
       </c>
       <c r="K274" s="12" t="n"/>
       <c r="L274" s="12" t="n">
-        <v>7.805429864253388</v>
+        <v>19.27409261576971</v>
       </c>
       <c r="M274" s="13" t="n"/>
       <c r="N274" s="13" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="K275" s="12" t="n"/>
       <c r="L275" s="12" t="n">
-        <v>5.293482175009001</v>
+        <v>9.308411214953271</v>
       </c>
       <c r="M275" s="13" t="n"/>
       <c r="N275" s="13" t="n"/>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="K276" s="12" t="n"/>
       <c r="L276" s="12" t="n">
-        <v>4.726368159203997</v>
+        <v>9.279688513951978</v>
       </c>
       <c r="M276" s="13" t="n"/>
       <c r="N276" s="13" t="n"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="K277" s="12" t="n"/>
       <c r="L277" s="12" t="n">
-        <v>4.378131126116336</v>
+        <v>8.416289592760172</v>
       </c>
       <c r="M277" s="13" t="n"/>
       <c r="N277" s="13" t="n"/>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="K278" s="12" t="n"/>
       <c r="L278" s="12" t="n">
-        <v>8.942091262533269</v>
+        <v>10.65156396134261</v>
       </c>
       <c r="M278" s="13" t="n"/>
       <c r="N278" s="13" t="n"/>
@@ -20824,7 +20824,7 @@
       </c>
       <c r="K281" s="12" t="n"/>
       <c r="L281" s="12" t="n">
-        <v>15.09794553272814</v>
+        <v>19.23774954627948</v>
       </c>
       <c r="M281" s="13" t="n"/>
       <c r="N281" s="13" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="K282" s="12" t="n"/>
       <c r="L282" s="12" t="n">
-        <v>1.367614879649892</v>
+        <v>4.807692307692313</v>
       </c>
       <c r="M282" s="13" t="n"/>
       <c r="N282" s="13" t="n"/>
@@ -20946,7 +20946,7 @@
       </c>
       <c r="K283" s="12" t="n"/>
       <c r="L283" s="12" t="n">
-        <v>10.29962546816479</v>
+        <v>15.26418786692758</v>
       </c>
       <c r="M283" s="13" t="n"/>
       <c r="N283" s="13" t="n"/>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="K285" s="12" t="n"/>
       <c r="L285" s="12" t="n">
-        <v>7.594495732450812</v>
+        <v>13.40187259041674</v>
       </c>
       <c r="M285" s="13" t="n"/>
       <c r="N285" s="13" t="n"/>
@@ -21131,7 +21131,7 @@
         <v>22.40231175706311</v>
       </c>
       <c r="L286" s="17" t="n">
-        <v>7.627118644067776</v>
+        <v>24.31736218444101</v>
       </c>
       <c r="M286" s="18" t="n">
         <v>0.1941506733753158</v>
@@ -21206,7 +21206,7 @@
         <v>230.3530552745098</v>
       </c>
       <c r="L287" s="17" t="n">
-        <v>8.723627768537145</v>
+        <v>23.28882712066311</v>
       </c>
       <c r="M287" s="18" t="n">
         <v>0.1840142778731264</v>
@@ -21281,7 +21281,7 @@
         <v>228.9219592503339</v>
       </c>
       <c r="L288" s="17" t="n">
-        <v>9.134935797751819</v>
+        <v>23.45077147308638</v>
       </c>
       <c r="M288" s="18" t="n">
         <v>0.1822958635431886</v>
@@ -21356,7 +21356,7 @@
         <v>229.4252547664068</v>
       </c>
       <c r="L289" s="17" t="n">
-        <v>8.073121665354677</v>
+        <v>23.68987436808649</v>
       </c>
       <c r="M289" s="18" t="n">
         <v>0.1772674373419185</v>
@@ -21431,7 +21431,7 @@
         <v>222.4733640314144</v>
       </c>
       <c r="L290" s="17" t="n">
-        <v>7.503698059079289</v>
+        <v>24.76200384955522</v>
       </c>
       <c r="M290" s="18" t="n">
         <v>0.1692023488282194</v>
@@ -21506,7 +21506,7 @@
         <v>23.4566490950615</v>
       </c>
       <c r="L291" s="17" t="n">
-        <v>8.229747106729546</v>
+        <v>23.95679921453118</v>
       </c>
       <c r="M291" s="18" t="n">
         <v>0.1680430358042399</v>
@@ -21581,7 +21581,7 @@
         <v>223.0050645185009</v>
       </c>
       <c r="L292" s="17" t="n">
-        <v>8.150413817920121</v>
+        <v>24.70954356846473</v>
       </c>
       <c r="M292" s="18" t="n">
         <v>0.1594459191525645</v>
@@ -21656,7 +21656,7 @@
         <v>220.9240431534428</v>
       </c>
       <c r="L293" s="17" t="n">
-        <v>7.551260048776087</v>
+        <v>23.05704836709383</v>
       </c>
       <c r="M293" s="18" t="n">
         <v>0.1499760706047594</v>
@@ -21731,7 +21731,7 @@
         <v>225.0260199003596</v>
       </c>
       <c r="L294" s="17" t="n">
-        <v>7.741388541852579</v>
+        <v>21.87452682582143</v>
       </c>
       <c r="M294" s="18" t="n">
         <v>0.137919932552608</v>
@@ -21806,7 +21806,7 @@
         <v>230.3450627377987</v>
       </c>
       <c r="L295" s="17" t="n">
-        <v>7.821253311330167</v>
+        <v>23.84277733439746</v>
       </c>
       <c r="M295" s="18" t="n">
         <v>0.123538431628378</v>
@@ -21881,7 +21881,7 @@
         <v>221.4144840009396</v>
       </c>
       <c r="L296" s="17" t="n">
-        <v>7.49447276993187</v>
+        <v>24.16740501381143</v>
       </c>
       <c r="M296" s="18" t="n">
         <v>0.1197309926688758</v>
@@ -21956,7 +21956,7 @@
         <v>231.2153603680001</v>
       </c>
       <c r="L297" s="17" t="n">
-        <v>7.520457202234065</v>
+        <v>21.32493038252967</v>
       </c>
       <c r="M297" s="18" t="n">
         <v>0.1073142582215872</v>
@@ -22031,7 +22031,7 @@
         <v>226.1758045655558</v>
       </c>
       <c r="L298" s="17" t="n">
-        <v>7.437287836705897</v>
+        <v>24.21632091340027</v>
       </c>
       <c r="M298" s="18" t="n">
         <v>0.1000828275172911</v>
@@ -22106,7 +22106,7 @@
         <v>227.2281747114946</v>
       </c>
       <c r="L299" s="17" t="n">
-        <v>8.182502102048939</v>
+        <v>19.27205308352848</v>
       </c>
       <c r="M299" s="18" t="n">
         <v>0.086997766498768</v>
@@ -22181,7 +22181,7 @@
         <v>22.65909280079883</v>
       </c>
       <c r="L300" s="17" t="n">
-        <v>7.16483516483517</v>
+        <v>23.31815882650481</v>
       </c>
       <c r="M300" s="18" t="n">
         <v>0.0811529360087937</v>
@@ -22256,7 +22256,7 @@
         <v>22.46109191082057</v>
       </c>
       <c r="L301" s="17" t="n">
-        <v>7.857142857142874</v>
+        <v>22.39108409321176</v>
       </c>
       <c r="M301" s="18" t="n">
         <v>0.07417002362553926</v>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="K302" s="17" t="n"/>
       <c r="L302" s="17" t="n">
-        <v>6.838304822487751</v>
+        <v>23.64821170969507</v>
       </c>
       <c r="M302" s="18" t="n">
         <v>-0.9886786544280333</v>
@@ -22400,7 +22400,7 @@
         <v>7045.726664889474</v>
       </c>
       <c r="L303" s="17" t="n">
-        <v>5.420054200542013</v>
+        <v>12.4277456647399</v>
       </c>
       <c r="M303" s="18" t="n">
         <v>-1.673476799703988</v>
@@ -22475,7 +22475,7 @@
         <v>24.32921462436839</v>
       </c>
       <c r="L304" s="17" t="n">
-        <v>3.747795414462085</v>
+        <v>8.633425669436745</v>
       </c>
       <c r="M304" s="18" t="n">
         <v>-1.726344789318005</v>
@@ -22550,7 +22550,7 @@
         <v>1273.129090959418</v>
       </c>
       <c r="L305" s="17" t="n">
-        <v>4.189998825233965</v>
+        <v>7.781738637284286</v>
       </c>
       <c r="M305" s="18" t="n">
         <v>-1.751170715497623</v>
@@ -22625,7 +22625,7 @@
         <v>65.56122591083897</v>
       </c>
       <c r="L306" s="17" t="n">
-        <v>6.352087114337568</v>
+        <v>9.430438842203536</v>
       </c>
       <c r="M306" s="18" t="n">
         <v>-1.753372388194087</v>
@@ -22735,17 +22735,17 @@
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t>GROWWPOWER</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="D3" s="22" t="inlineStr">
         <is>
-          <t>Groww BSE Power ETF</t>
+          <t>Mirae Asset Nifty Energy ETF</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -23006,12 +23006,12 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>GROWWPOWER</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>Groww BSE Power ETF</t>
+          <t>Mirae Asset Nifty Energy ETF</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>GROWWPOWER</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -23207,7 +23207,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -23216,12 +23216,12 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>GROWWPOWER</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Groww BSE Power ETF</t>
+          <t>Mirae Asset Nifty Energy ETF</t>
         </is>
       </c>
       <c r="F3" s="36" t="n">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Sort: 3M Sharpe (partial regime sort)  |  Sector=ENERGY (1/1)  |  3M Sharpe=3.379</t>
+          <t>Sort: Investable composite rank (WTD_SHARPE)  |  Sector=ENERGY (1/1)  |  3M Sharpe=2.588</t>
         </is>
       </c>
     </row>
@@ -23260,7 +23260,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Sort: 3M Sharpe (partial regime sort)  |  Sector=INTERNATIONAL (1/1)  |  3M Sharpe=3.243</t>
+          <t>Sort: Investable composite rank (WTD_SHARPE)  |  Sector=INTERNATIONAL (1/1)  |  3M Sharpe=3.243</t>
         </is>
       </c>
     </row>
@@ -23291,7 +23291,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Sort: 3M Sharpe (partial regime sort)  |  Sector=PSE (1/1)  |  3M Sharpe=2.855</t>
+          <t>Sort: Investable composite rank (WTD_SHARPE)  |  Sector=PSE (1/1)  |  3M Sharpe=2.855</t>
         </is>
       </c>
     </row>
